--- a/inputs/es/LiST countries/SSD_databook.xlsx
+++ b/inputs/es/LiST countries/SSD_databook.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\es\LiST countries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41824AB5-1351-4EA5-AA45-3734F4BF23BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07E5268F-9CEA-46CC-A9DD-5628CA7BF666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Causas de muerte" sheetId="3" r:id="rId3"/>
     <sheet name="Distribución estado nutricional" sheetId="4" r:id="rId4"/>
     <sheet name="Distribución de lactancia" sheetId="5" r:id="rId5"/>
-    <sheet name="Tendencias temporales" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Tendencias temporales" sheetId="6" r:id="rId6"/>
     <sheet name="Pérdida económica" sheetId="7" r:id="rId7"/>
     <sheet name="Paquetes de IYCF" sheetId="8" r:id="rId8"/>
     <sheet name="Tratamiento de la MAS" sheetId="9" r:id="rId9"/>
@@ -91,7 +91,7 @@
     <definedName name="term_SGA">'Entradas de población-año base'!$C$47</definedName>
     <definedName name="U5_mortality">'Entradas de población-año base'!$C$39</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -678,8 +678,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
+OR = 0.89 for stunting [Panjwani et al. 2017 J Nutr</t>
         </r>
       </text>
     </comment>
@@ -692,8 +691,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
+OR = 0.89 for stunting [Panjwani et al. 2017 J Nutr</t>
         </r>
       </text>
     </comment>
@@ -834,35 +832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F29" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000010000000}">
+    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -876,7 +846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000011000000}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -890,7 +860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000012000000}">
+    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000010000000}">
       <text>
         <r>
           <rPr>
@@ -904,7 +874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A34" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000013000000}">
+    <comment ref="A34" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000011000000}">
       <text>
         <r>
           <rPr>
@@ -917,7 +887,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000014000000}">
+    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000012000000}">
       <text>
         <r>
           <rPr>
@@ -930,7 +900,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000015000000}">
+    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000013000000}">
       <text>
         <r>
           <rPr>
@@ -943,7 +913,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
+    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000014000000}">
       <text>
         <r>
           <rPr>
@@ -956,7 +926,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
+    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000015000000}">
       <text>
         <r>
           <rPr>
@@ -969,35 +939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E52" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F52" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000019000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001A000000}">
+    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
       <text>
         <r>
           <rPr>
@@ -1011,7 +953,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001B000000}">
+    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
       <text>
         <r>
           <rPr>
@@ -1025,7 +967,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001C000000}">
+    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
       <text>
         <r>
           <rPr>
@@ -1561,8 +1503,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -1732,8 +1673,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -1746,8 +1686,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -1760,8 +1699,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -1774,8 +1712,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2138,8 +2075,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Peña‐Rosas et al 2019, anemia RR 0.72 (0.54-0.97)
-If no data for anaemia prev. the use RR otherwise convert RR to OR using prev.</t>
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -2152,7 +2088,8 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Insufficient published research on the intervention’s effect on the outcome.</t>
+Insufficient published research on the intervention’s effect on the outcome.
+Thereofre, set effect of rice = effect of wheat</t>
         </r>
       </text>
     </comment>
@@ -2165,8 +2102,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Larson et al 2021, RR 0.80 (0.70-0.92)
-If no data for anaemia prev. the use RR otherwise convert RR to OR using prev.</t>
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -2192,8 +2128,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -2366,8 +2301,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2380,8 +2314,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2394,8 +2327,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2408,8 +2340,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2660,7 +2591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
+    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
       <text>
         <r>
           <rPr>
@@ -2669,12 +2600,37 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
       <text>
         <r>
           <rPr>
@@ -2688,7 +2644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
+    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
       <text>
         <r>
           <rPr>
@@ -2702,7 +2658,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
+    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
       <text>
         <r>
           <rPr>
@@ -2716,7 +2672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
+    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
       <text>
         <r>
           <rPr>
@@ -2730,7 +2686,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
       <text>
         <r>
           <rPr>
@@ -2744,7 +2700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
+    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
       <text>
         <r>
           <rPr>
@@ -2758,7 +2714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
+    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
       <text>
         <r>
           <rPr>
@@ -2772,7 +2728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
+    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
       <text>
         <r>
           <rPr>
@@ -2786,7 +2742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
+    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
       <text>
         <r>
           <rPr>
@@ -2800,7 +2756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
+    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
       <text>
         <r>
           <rPr>
@@ -2814,7 +2770,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
+    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
       <text>
         <r>
           <rPr>
@@ -2828,7 +2784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
+    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
       <text>
         <r>
           <rPr>
@@ -2842,7 +2798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
       <text>
         <r>
           <rPr>
@@ -2856,7 +2812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
       <text>
         <r>
           <rPr>
@@ -2870,7 +2826,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
+    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
       <text>
         <r>
           <rPr>
@@ -2884,7 +2840,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
+    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
       <text>
         <r>
           <rPr>
@@ -2898,7 +2854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
+    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
       <text>
         <r>
           <rPr>
@@ -2911,7 +2867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
+    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
       <text>
         <r>
           <rPr>
@@ -2924,7 +2880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
+    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
       <text>
         <r>
           <rPr>
@@ -2937,7 +2893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
+    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
       <text>
         <r>
           <rPr>
@@ -2950,7 +2906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
+    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
       <text>
         <r>
           <rPr>
@@ -2963,7 +2919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
+    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
       <text>
         <r>
           <rPr>
@@ -2976,7 +2932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
+    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
       <text>
         <r>
           <rPr>
@@ -2989,7 +2945,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
+    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
       <text>
         <r>
           <rPr>
@@ -3002,7 +2958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
+    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
       <text>
         <r>
           <rPr>
@@ -3011,12 +2967,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
       <text>
         <r>
           <rPr>
@@ -3025,12 +2980,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
       <text>
         <r>
           <rPr>
@@ -3039,12 +2993,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
       <text>
         <r>
           <rPr>
@@ -3053,12 +3006,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
       <text>
         <r>
           <rPr>
@@ -3072,7 +3024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
+    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
       <text>
         <r>
           <rPr>
@@ -3086,7 +3038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
+    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
       <text>
         <r>
           <rPr>
@@ -3100,7 +3052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
+    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
       <text>
         <r>
           <rPr>
@@ -3114,7 +3066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
+    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
       <text>
         <r>
           <rPr>
@@ -3128,7 +3080,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
+    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
       <text>
         <r>
           <rPr>
@@ -3142,7 +3094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
+    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
       <text>
         <r>
           <rPr>
@@ -3156,7 +3108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
+    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
       <text>
         <r>
           <rPr>
@@ -3170,7 +3122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
+    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
       <text>
         <r>
           <rPr>
@@ -3184,7 +3136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
+    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
       <text>
         <r>
           <rPr>
@@ -3198,7 +3150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
+    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
       <text>
         <r>
           <rPr>
@@ -3212,7 +3164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
+    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
       <text>
         <r>
           <rPr>
@@ -3226,7 +3178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
+    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
       <text>
         <r>
           <rPr>
@@ -3240,7 +3192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
+    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
       <text>
         <r>
           <rPr>
@@ -3253,7 +3205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
+    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
       <text>
         <r>
           <rPr>
@@ -3266,7 +3218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
+    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
       <text>
         <r>
           <rPr>
@@ -3279,7 +3231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000081000000}">
       <text>
         <r>
           <rPr>
@@ -3292,7 +3244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000082000000}">
       <text>
         <r>
           <rPr>
@@ -3302,6 +3254,32 @@
           </rPr>
           <t xml:space="preserve">Tharindu Wickramaarachchi:
 Wessells et al 2022, iron deficiency anemia), PR 0.36 (0.30-0.44) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000083000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000084000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -4373,7 +4351,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Nick Scott:
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -5023,7 +5001,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Nick Scott:
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -5673,7 +5651,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Nick Scott:
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -6941,9 +6919,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6955,9 +6932,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6969,9 +6945,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6983,9 +6958,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7118,68 +7092,12 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000010000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000012000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
           <t xml:space="preserve">Tharindu Wickramaarachchi:
 Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000013000000}">
+    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -7192,7 +7110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000014000000}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000010000000}">
       <text>
         <r>
           <rPr>
@@ -7205,7 +7123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000015000000}">
+    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000011000000}">
       <text>
         <r>
           <rPr>
@@ -7218,6 +7136,58 @@
         </r>
       </text>
     </comment>
+    <comment ref="F64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000012000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000013000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000015000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A89" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-000016000000}">
       <text>
         <r>
@@ -7239,9 +7209,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7253,9 +7222,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7267,9 +7235,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7281,9 +7248,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7370,7 +7336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="341">
   <si>
     <t>Field</t>
   </si>
@@ -9313,7 +9279,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="41">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -9322,7 +9288,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="42">
-        <v>2030</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -9340,7 +9306,7 @@
         <v>23</v>
       </c>
       <c r="C7" s="43">
-        <v>1463471.375</v>
+        <v>1471007.40625</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9372,7 +9338,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="45">
-        <v>0.17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9380,7 +9346,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="45">
-        <v>0.47599999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9414,7 +9380,7 @@
         <v>30</v>
       </c>
       <c r="C17" s="45">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9422,7 +9388,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="45">
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9430,7 +9396,7 @@
         <v>29</v>
       </c>
       <c r="C19" s="45">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9439,7 +9405,7 @@
       </c>
       <c r="C20" s="46">
         <f>1-frac_rice-frac_wheat-frac_maize</f>
-        <v>0.20000000000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9498,7 +9464,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="45">
-        <v>0.19150365160233301</v>
+        <v>0.22259625228416199</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9506,7 +9472,7 @@
         <v>63</v>
       </c>
       <c r="C30" s="99">
-        <v>6.8825578474898896E-2</v>
+        <v>6.9957740305893898E-2</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9514,7 +9480,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="99">
-        <v>0.12157427723799701</v>
+        <v>0.118524449608315</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9522,7 +9488,7 @@
         <v>11</v>
       </c>
       <c r="C32" s="99">
-        <v>0.61809649268477107</v>
+        <v>0.58892155780162903</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.25">
@@ -9531,7 +9497,7 @@
       </c>
       <c r="C33" s="48">
         <f>SUM(C29:C32)</f>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9551,7 +9517,7 @@
         <v>38</v>
       </c>
       <c r="C37" s="43">
-        <v>38.604565867455698</v>
+        <v>39.626449999999998</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9559,7 +9525,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="43">
-        <v>62.3710703861653</v>
+        <v>63.756</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="13"/>
@@ -9569,7 +9535,7 @@
         <v>61</v>
       </c>
       <c r="C39" s="43">
-        <v>96.229298685854801</v>
+        <v>98.689639999999997</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
@@ -9579,7 +9545,7 @@
         <v>36</v>
       </c>
       <c r="C40" s="100">
-        <v>11.5</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9595,7 +9561,7 @@
         <v>57</v>
       </c>
       <c r="C42" s="43">
-        <v>28.81322853</v>
+        <v>25.841349999999998</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9612,7 +9578,7 @@
         <v>52</v>
       </c>
       <c r="C45" s="45">
-        <v>2.8654000000000002E-3</v>
+        <v>7.9325000000000003E-3</v>
       </c>
       <c r="D45" s="12"/>
     </row>
@@ -9621,7 +9587,7 @@
         <v>51</v>
       </c>
       <c r="C46" s="45">
-        <v>8.5688099999999989E-2</v>
+        <v>8.5233500000000004E-2</v>
       </c>
       <c r="D46" s="12"/>
     </row>
@@ -9630,7 +9596,7 @@
         <v>59</v>
       </c>
       <c r="C47" s="45">
-        <v>0.14243310000000001</v>
+        <v>7.3456999999999995E-2</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="13"/>
@@ -9640,7 +9606,7 @@
         <v>58</v>
       </c>
       <c r="C48" s="46">
-        <v>0.76901340000000007</v>
+        <v>0.83337700000000003</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="12"/>
@@ -9744,7 +9710,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="UuaFxCXI3t768E5/G4fqWDxPLI1abqIG8J4ILcQupmQ14jm7Cmmvax9Vsrfj2OHIm5H8qGD4FlcQ5HayVFWXLw==" saltValue="tvXLBsizQxWluwfaX2cjyw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="9JYIy73bNfgHDgpUfbE37+ud40AFZgUaSEgpnLG0YHZbE5urEOqMytHU74adj8e3X73RV4YtCYXYasMDQ/9c4A==" saltValue="fPXgj66Lv53lBxgBGJo8gA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -9776,7 +9742,7 @@
       </c>
       <c r="B1" s="22" t="str">
         <f>"Cobertura de referencia ("&amp;start_year&amp;")"</f>
-        <v>Cobertura de referencia (2021)</v>
+        <v>Cobertura de referencia (2024)</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>194</v>
@@ -9822,7 +9788,7 @@
         <v>166</v>
       </c>
       <c r="B3" s="45">
-        <v>0</v>
+        <v>9.995594406000001E-2</v>
       </c>
       <c r="C3" s="98">
         <v>0.95</v>
@@ -9874,7 +9840,7 @@
         <v>0.95</v>
       </c>
       <c r="D5" s="56">
-        <v>2.8660164968156591E-2</v>
+        <v>3.0405569014717328E-2</v>
       </c>
       <c r="E5" s="56" t="s">
         <v>183</v>
@@ -10121,7 +10087,7 @@
         <v>180</v>
       </c>
       <c r="B16" s="45">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="C16" s="98">
         <v>0.95</v>
@@ -10144,7 +10110,7 @@
         <v>181</v>
       </c>
       <c r="B17" s="98">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="C17" s="98">
         <v>0.95</v>
@@ -10167,7 +10133,7 @@
         <v>151</v>
       </c>
       <c r="B18" s="98">
-        <v>0</v>
+        <v>1.5453490249780001E-2</v>
       </c>
       <c r="C18" s="98">
         <v>0.95</v>
@@ -10190,7 +10156,7 @@
         <v>152</v>
       </c>
       <c r="B19" s="98">
-        <v>0</v>
+        <v>0.16055179999999999</v>
       </c>
       <c r="C19" s="98">
         <v>0.95</v>
@@ -10236,7 +10202,7 @@
         <v>182</v>
       </c>
       <c r="B21" s="45">
-        <v>0.15741054713725999</v>
+        <v>4.4852499999999997E-2</v>
       </c>
       <c r="C21" s="98">
         <v>0.95</v>
@@ -10282,7 +10248,7 @@
         <v>185</v>
       </c>
       <c r="B23" s="98">
-        <v>1.345673084E-2</v>
+        <v>0</v>
       </c>
       <c r="C23" s="98">
         <v>0.95</v>
@@ -10305,7 +10271,7 @@
         <v>188</v>
       </c>
       <c r="B24" s="45">
-        <v>0</v>
+        <v>0.11710145397736001</v>
       </c>
       <c r="C24" s="98">
         <v>0.95</v>
@@ -10397,7 +10363,7 @@
         <v>192</v>
       </c>
       <c r="B28" s="45">
-        <v>0.3860053</v>
+        <v>9.1830699727579998E-2</v>
       </c>
       <c r="C28" s="98">
         <v>0.95</v>
@@ -10466,7 +10432,7 @@
         <v>164</v>
       </c>
       <c r="B31" s="45">
-        <v>0.46089999999999998</v>
+        <v>0.9</v>
       </c>
       <c r="C31" s="98">
         <v>0.95</v>
@@ -10489,7 +10455,7 @@
         <v>196</v>
       </c>
       <c r="B32" s="45">
-        <v>0.41144239999999999</v>
+        <v>0</v>
       </c>
       <c r="C32" s="98">
         <v>0.95</v>
@@ -10535,7 +10501,7 @@
         <v>198</v>
       </c>
       <c r="B34" s="45">
-        <v>0.113216843085857</v>
+        <v>0.9</v>
       </c>
       <c r="C34" s="98">
         <v>0.95</v>
@@ -10581,7 +10547,7 @@
         <v>200</v>
       </c>
       <c r="B36" s="45">
-        <v>0</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="C36" s="98">
         <v>0.95</v>
@@ -10604,7 +10570,7 @@
         <v>201</v>
       </c>
       <c r="B37" s="45">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="C37" s="98">
         <v>0.95</v>
@@ -10627,7 +10593,7 @@
         <v>202</v>
       </c>
       <c r="B38" s="45">
-        <v>3.0882237479090701E-2</v>
+        <v>0.3860053</v>
       </c>
       <c r="C38" s="98">
         <v>0.95</v>
@@ -10650,7 +10616,7 @@
         <v>203</v>
       </c>
       <c r="B39" s="45">
-        <v>0.49399999999999999</v>
+        <v>0</v>
       </c>
       <c r="C39" s="98">
         <v>0.95</v>
@@ -10669,7 +10635,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="j+9tIHDd/VFSrTIDU96Un3vjOVq5tvuvF5MHGFmObet1jebmP55GVttCR/iw8tmFLcQNWb3AzvWtEhy2VpyfrA==" saltValue="wV+f1Jk+5v16D1Nez+f9wA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="tfRVkFICe0i9H2ULz19k027xVtkP1YodjB4a2wyZwYGaiqeQsVbm6QXbybHGl4pYCMAtP1p72qM+4y9i3OlYVw==" saltValue="XZojYARCnc0U8jEn0wWJWg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10702,7 +10668,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
         <v>178</v>
       </c>
@@ -10711,7 +10677,7 @@
       </c>
       <c r="C2" s="47"/>
     </row>
-    <row r="3" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="57" t="s">
         <v>179</v>
       </c>
@@ -10720,7 +10686,7 @@
       </c>
       <c r="C3" s="47"/>
     </row>
-    <row r="4" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="57" t="s">
         <v>193</v>
       </c>
@@ -10729,7 +10695,7 @@
       </c>
       <c r="C4" s="47"/>
     </row>
-    <row r="5" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="57" t="s">
         <v>190</v>
       </c>
@@ -10738,83 +10704,99 @@
       </c>
       <c r="C5" s="47"/>
     </row>
-    <row r="6" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="57"/>
-      <c r="B6" s="58"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>204</v>
+      </c>
       <c r="C6" s="58"/>
     </row>
-    <row r="7" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="57"/>
-      <c r="B7" s="58"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>204</v>
+      </c>
       <c r="C7" s="58"/>
     </row>
-    <row r="8" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="57" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" s="58" t="s">
+        <v>204</v>
+      </c>
       <c r="C8" s="58"/>
     </row>
-    <row r="9" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="57"/>
-      <c r="B9" s="58"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>204</v>
+      </c>
       <c r="C9" s="58"/>
     </row>
-    <row r="10" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="57"/>
       <c r="B10" s="58"/>
       <c r="C10" s="58"/>
     </row>
-    <row r="11" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="59"/>
       <c r="B11" s="58"/>
       <c r="C11" s="58"/>
     </row>
-    <row r="12" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="59"/>
       <c r="B12" s="58"/>
       <c r="C12" s="58"/>
     </row>
-    <row r="13" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="59"/>
       <c r="B13" s="58"/>
       <c r="C13" s="58"/>
     </row>
-    <row r="14" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="59"/>
       <c r="B14" s="58"/>
       <c r="C14" s="58"/>
     </row>
-    <row r="15" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="59"/>
       <c r="B15" s="58"/>
       <c r="C15" s="58"/>
     </row>
-    <row r="16" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="59"/>
       <c r="B16" s="58"/>
       <c r="C16" s="58"/>
     </row>
-    <row r="17" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="59"/>
       <c r="B17" s="58"/>
       <c r="C17" s="58"/>
     </row>
-    <row r="18" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="59"/>
       <c r="B18" s="58"/>
       <c r="C18" s="58"/>
     </row>
-    <row r="19" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="57"/>
       <c r="B19" s="58"/>
       <c r="C19" s="58"/>
     </row>
-    <row r="20" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="57"/>
       <c r="B20" s="58"/>
       <c r="C20" s="58"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="U6zlZ3UiHB/9WuH82PawPyq9EUVIsmopRogCyBr2FxMJez3q8sir6c7qdzgSblSYcZPoEDN7vgFANyg9R0Wu8w==" saltValue="DJvjbLmfA+I0IRaFKMbybw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8KvhZyxn0FdEbkBAfQjNv2L6X/kVi8n5OoTu4UGS2KCD/UUs6NLVBqaYyQOeFOkDuz5IHJsCjz8+G52vHp/gog==" saltValue="ZagZvr6e/tpfZLrCSouIrg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -10839,78 +10821,78 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="33"/>
     </row>
-    <row r="11" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
     </row>
-    <row r="12" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
     </row>
-    <row r="13" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
     </row>
-    <row r="14" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
     </row>
-    <row r="15" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
     </row>
-    <row r="16" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
     </row>
-    <row r="17" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="33"/>
     </row>
-    <row r="18" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="33"/>
     </row>
-    <row r="19" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="33"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="4otM8FmLKwMriNdpiraO5m+j/mYf/5jXBEU+eYpFhHzqTeMH+u5l0plc0hl3V/R8o8PSN0I47yOjYTsUrUMdjA==" saltValue="mJUeZ48nvHnMSV9hrbrE+Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="oEBI/u0LYXRVvR2bwllNROSUvh02e9qpkPEZ1WO+MFbxQZZ4xm17l870aWBzSx81oucAEab1zCxlbRKbyFsNFQ==" saltValue="+leMMn+FxMoOgk9m1Co9Hg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -10975,23 +10957,23 @@
       </c>
       <c r="B3" s="21">
         <f>frac_mam_1month * 2.6</f>
-        <v>0.29120254665613282</v>
+        <v>0.28802462000000001</v>
       </c>
       <c r="C3" s="21">
         <f>frac_mam_1_5months * 2.6</f>
-        <v>0.29120254665613282</v>
+        <v>0.28802462000000001</v>
       </c>
       <c r="D3" s="21">
         <f>frac_mam_6_11months * 2.6</f>
-        <v>0.40556049048900583</v>
+        <v>0.40525783999999998</v>
       </c>
       <c r="E3" s="21">
         <f>frac_mam_12_23months * 2.6</f>
-        <v>0.3329371273517614</v>
+        <v>0.33359144000000007</v>
       </c>
       <c r="F3" s="21">
         <f>frac_mam_24_59months * 2.6</f>
-        <v>0.32151324450969621</v>
+        <v>0.32582003999999998</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11000,27 +10982,27 @@
       </c>
       <c r="B4" s="21">
         <f>frac_sam_1month * 2.6</f>
-        <v>0.22625849545001975</v>
+        <v>0.22378927999999998</v>
       </c>
       <c r="C4" s="21">
         <f>frac_sam_1_5months * 2.6</f>
-        <v>0.22625849545001975</v>
+        <v>0.22378927999999998</v>
       </c>
       <c r="D4" s="21">
         <f>frac_sam_6_11months * 2.6</f>
-        <v>0.299175317585469</v>
+        <v>0.29543254000000002</v>
       </c>
       <c r="E4" s="21">
         <f>frac_sam_12_23months * 2.6</f>
-        <v>0.25278518199920652</v>
+        <v>0.26182988000000001</v>
       </c>
       <c r="F4" s="21">
         <f>frac_sam_24_59months * 2.6</f>
-        <v>0.24493354111909882</v>
+        <v>0.25237186</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="MMTnw9IwvcZ+mtNUdWmyAUFdv45sULnCWyn0R1/SjUeqfx5zNHxiiir+ogZHP9CoV756r6Hn8O0oXFLR2i3KkA==" saltValue="CKC5h8dB6gxaB8xfFv6j+w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="iEa1SU/QYNLrr6WeTqVV7MdKMF5XrPZVjtKM5lmWFfQJBpC0wYmGhR7lBspeP2PdyeN6XGFswn4Ge4F22C705g==" saltValue="8y+iZFvRPXxFdPTIuxFqeg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -11473,19 +11455,19 @@
       </c>
       <c r="D10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.47599999999999998</v>
+        <v>1</v>
       </c>
       <c r="E10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.47599999999999998</v>
+        <v>1</v>
       </c>
       <c r="F10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.47599999999999998</v>
+        <v>1</v>
       </c>
       <c r="G10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.47599999999999998</v>
+        <v>1</v>
       </c>
       <c r="H10" s="61">
         <v>0</v>
@@ -11819,19 +11801,19 @@
       </c>
       <c r="H18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="I18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="J18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="K18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="L18" s="61">
         <v>0</v>
@@ -12298,47 +12280,47 @@
       </c>
       <c r="E30" s="60">
         <f t="shared" ref="E30:O30" si="0">frac_maize</f>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="J30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="L30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="M30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="N30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="O30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12353,47 +12335,47 @@
       </c>
       <c r="E31" s="60">
         <f t="shared" ref="E31:O31" si="1">frac_rice</f>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="F31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="G31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="H31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="I31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="J31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="K31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="L31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="M31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="N31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="O31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12408,47 +12390,47 @@
       </c>
       <c r="E32" s="60">
         <f t="shared" ref="E32:O32" si="2">frac_wheat</f>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="F32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="G32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="H32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="I32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="J32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="K32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="L32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="M32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="N32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="O32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="33" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12776,7 +12758,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="GyXzE3vap04prJQXT4s4AbTL/LleQSlyeB1HypeW6aqyEAFxn/SL2xVpA6qhwCzw+2IKSUvlp4y8aSwVTbTsLw==" saltValue="4fcz171vQ0n20xIYvKA0BQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Zco+kqvCO0WzQA7FkDyNOIwTJURcAFUpbLj7303xGqUIWRnFqGueUn5UWnfrGpqeo+SVhs7PxbWXMreMfi+wWw==" saltValue="ieKEG01x1DrFVnhM1J6Hww==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12808,7 +12790,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="J01lSI1PK/UI/i73zm3GHA1+3t6hYOvW7n6pZDSaVtt/5An+/Vb/o3Kt4t3aURXHkrJCB8MTm+oxrqNxdM4diQ==" saltValue="bBAKssMvhd15oU8rNdL3Sg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8f1w6UoxlnXUWSk64Iy0Jf8GHtZS0wjuFlBXGPKq9FUrpOB+dUJT48R5Uf908TezX7WMyPLTlGbPoUUH+jvPXQ==" saltValue="aAt7RlnS2QEvHpMqH9qsvg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13009,7 +12991,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="YzsEs1WteNtfsni2rN7xFtMw3dCOcvNubaZL9KiVYesSb+JB4yfKStQFvQSbSrh9dG5Xb1n3Fq72Tih8J8V7zg==" saltValue="BJyIXqLYW/Cjq8PInQBbZg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jLJhq/VeI7HLa9H2CprwFWRsz3OAkSjUxw4qZNbdqwtV83rbwwf+4LWOSOIrt0A83svpqXQkm1hywGBPxI3XCw==" saltValue="1zrjBe+Ac1AwjigCgN8eJg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -14819,7 +14801,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8AGlFlp0jo61vcYqpgsg9SWLKaNo8tVzaM1UrmB6dXEznYqDqwV/Ig2MFr7GVuqlCGVPDUcVJyvX3t4Bx4bscw==" saltValue="mv+IOtxcjykHbhG+M8ZgiQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="WVGZ9yjtT58sWo0Byg78tnlRVhBgnwW5Jle64jty6FoRubzwPolcIrPMyi2PNvrkMZNAmOeU2DrMmxe7fU31KQ==" saltValue="mpJ/DiCIwlm7AFhulbQHYw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14881,7 +14863,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>165</v>
       </c>
@@ -14898,7 +14880,7 @@
       <c r="J2" s="87"/>
       <c r="K2" s="87"/>
     </row>
-    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>166</v>
       </c>
@@ -14915,7 +14897,7 @@
       <c r="J3" s="87"/>
       <c r="K3" s="87"/>
     </row>
-    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>167</v>
       </c>
@@ -14932,7 +14914,7 @@
       <c r="J4" s="87"/>
       <c r="K4" s="87"/>
     </row>
-    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>169</v>
       </c>
@@ -14949,7 +14931,7 @@
       <c r="J5" s="87"/>
       <c r="K5" s="87"/>
     </row>
-    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>170</v>
       </c>
@@ -14968,7 +14950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>171</v>
       </c>
@@ -14987,7 +14969,7 @@
       <c r="J7" s="87"/>
       <c r="K7" s="87"/>
     </row>
-    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>172</v>
       </c>
@@ -15006,7 +14988,7 @@
       <c r="J8" s="87"/>
       <c r="K8" s="87"/>
     </row>
-    <row r="9" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>173</v>
       </c>
@@ -15025,7 +15007,7 @@
       <c r="J9" s="87"/>
       <c r="K9" s="87"/>
     </row>
-    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>174</v>
       </c>
@@ -15042,7 +15024,7 @@
       <c r="J10" s="87"/>
       <c r="K10" s="87"/>
     </row>
-    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>175</v>
       </c>
@@ -15059,7 +15041,7 @@
       <c r="J11" s="87"/>
       <c r="K11" s="87"/>
     </row>
-    <row r="12" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>176</v>
       </c>
@@ -15076,7 +15058,7 @@
       <c r="J12" s="87"/>
       <c r="K12" s="87"/>
     </row>
-    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>177</v>
       </c>
@@ -15093,7 +15075,7 @@
       <c r="J13" s="87"/>
       <c r="K13" s="87"/>
     </row>
-    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>178</v>
       </c>
@@ -15112,7 +15094,7 @@
       <c r="J14" s="87"/>
       <c r="K14" s="87"/>
     </row>
-    <row r="15" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>179</v>
       </c>
@@ -15131,7 +15113,7 @@
       <c r="J15" s="87"/>
       <c r="K15" s="87"/>
     </row>
-    <row r="16" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>180</v>
       </c>
@@ -15152,7 +15134,7 @@
       <c r="J16" s="87"/>
       <c r="K16" s="87"/>
     </row>
-    <row r="17" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>181</v>
       </c>
@@ -15169,7 +15151,7 @@
       <c r="J17" s="87"/>
       <c r="K17" s="87"/>
     </row>
-    <row r="18" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>151</v>
       </c>
@@ -15188,7 +15170,7 @@
       <c r="J18" s="87"/>
       <c r="K18" s="87"/>
     </row>
-    <row r="19" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>152</v>
       </c>
@@ -15207,7 +15189,7 @@
       <c r="J19" s="87"/>
       <c r="K19" s="87"/>
     </row>
-    <row r="20" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>153</v>
       </c>
@@ -15226,7 +15208,7 @@
       <c r="J20" s="87"/>
       <c r="K20" s="87"/>
     </row>
-    <row r="21" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>182</v>
       </c>
@@ -15245,7 +15227,7 @@
       <c r="J21" s="87"/>
       <c r="K21" s="87"/>
     </row>
-    <row r="22" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>184</v>
       </c>
@@ -15582,7 +15564,7 @@
       <c r="K39" s="87"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+rDJwLmMTw/LFIcRIwnNYhwkyn635bf+0MZoDsIBKuebiXC1DTWy2mz2sKUwwnGYEZSvr35FaWpqgqxCdKtCnw==" saltValue="enKNhHrZgNSHOV83Bxzh6A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="f+4+onOsDivsoaJRDR2mrsXq8eHIoWQhubNDWwvVa5rUopECyl3gD8v5hsNrjlFJvEsI+6qITSvjn9681jYUUA==" saltValue="4RuLuZQOfDTd3XiiwBl3mA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15644,7 +15626,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>78</v>
       </c>
@@ -15673,7 +15655,7 @@
       <c r="J2" s="87"/>
       <c r="K2" s="87"/>
     </row>
-    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>74</v>
       </c>
@@ -15702,7 +15684,7 @@
       <c r="J3" s="87"/>
       <c r="K3" s="87"/>
     </row>
-    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>77</v>
       </c>
@@ -15731,7 +15713,7 @@
       <c r="J4" s="87"/>
       <c r="K4" s="87"/>
     </row>
-    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>75</v>
       </c>
@@ -15760,7 +15742,7 @@
       <c r="J5" s="87"/>
       <c r="K5" s="87"/>
     </row>
-    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>76</v>
       </c>
@@ -15789,7 +15771,7 @@
       <c r="J6" s="87"/>
       <c r="K6" s="87"/>
     </row>
-    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>113</v>
       </c>
@@ -15810,7 +15792,7 @@
       <c r="J7" s="87"/>
       <c r="K7" s="87"/>
     </row>
-    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>114</v>
       </c>
@@ -15831,7 +15813,7 @@
       <c r="J8" s="87"/>
       <c r="K8" s="87"/>
     </row>
-    <row r="9" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>115</v>
       </c>
@@ -15852,7 +15834,7 @@
       <c r="J9" s="87"/>
       <c r="K9" s="87"/>
     </row>
-    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>116</v>
       </c>
@@ -15873,7 +15855,7 @@
       <c r="J10" s="87"/>
       <c r="K10" s="87"/>
     </row>
-    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>68</v>
       </c>
@@ -15894,7 +15876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>69</v>
       </c>
@@ -15913,7 +15895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>70</v>
       </c>
@@ -15932,7 +15914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>71</v>
       </c>
@@ -15952,7 +15934,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ODw+HCvPu7hdDjMg7/QuLEiMVQMXQjNjN8Id17WFf0nDwbgUyUbE/wPVCpbKbhTeTXS4Vl2fUjxpdEVLm9Ynbw==" saltValue="8MU3T6kUxMSOUS69bKnjkA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="UHbMnUOFbzjCxVTOV3FQWKV72TgLWjqCiR2udoxXaDeNsGOpG+Rvvft2qsYKm9RztLi4EaOfpWi3/hLpY2RN8A==" saltValue="wUpbHkdLldVkZ3CWdvrf8A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16003,360 +15985,398 @@
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>start_year</f>
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B2" s="49">
-        <v>474679.08799999999</v>
+        <v>326409</v>
       </c>
       <c r="C2" s="49">
-        <v>739000</v>
+        <v>858169.50000000012</v>
       </c>
       <c r="D2" s="49">
-        <v>1225000</v>
+        <v>887619</v>
       </c>
       <c r="E2" s="49">
-        <v>1540000</v>
+        <v>516767.5</v>
       </c>
       <c r="F2" s="49">
-        <v>1553000</v>
+        <v>485674</v>
       </c>
       <c r="G2" s="17">
-        <f t="shared" ref="G2:G11" si="0">C2+D2+E2+F2</f>
-        <v>5057000</v>
+        <f t="shared" ref="G2:G13" si="0">C2+D2+E2+F2</f>
+        <v>2748230</v>
       </c>
       <c r="H2" s="17">
-        <f t="shared" ref="H2:H11" si="1">(B2 + stillbirth*B2/(1000-stillbirth))/(1-abortion)</f>
-        <v>555411.24569582019</v>
+        <f t="shared" ref="H2:H13" si="1">(B2 + stillbirth*B2/(1000-stillbirth))/(1-abortion)</f>
+        <v>380758.63534324535</v>
       </c>
       <c r="I2" s="17">
-        <f t="shared" ref="I2:I11" si="2">G2-H2</f>
-        <v>4501588.7543041799</v>
+        <f t="shared" ref="I2:I13" si="2">G2-H2</f>
+        <v>2367471.3646567548</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f t="shared" ref="A3:A40" si="3">IF($A$2+ROW(A3)-2&lt;=end_year,A2+1,"")</f>
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B3" s="49">
-        <v>480844.47639999999</v>
+        <v>333369</v>
       </c>
       <c r="C3" s="50">
-        <v>756000</v>
+        <v>886754.00000000012</v>
       </c>
       <c r="D3" s="50">
-        <v>1257000</v>
+        <v>955679.5</v>
       </c>
       <c r="E3" s="50">
-        <v>1519000</v>
+        <v>510816.50000000012</v>
       </c>
       <c r="F3" s="50">
-        <v>1575000</v>
+        <v>487057</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" si="0"/>
-        <v>5107000</v>
+        <v>2840307</v>
       </c>
       <c r="H3" s="17">
         <f t="shared" si="1"/>
-        <v>562625.22696866398</v>
+        <v>388877.5294362054</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" si="2"/>
-        <v>4544374.7730313363</v>
+        <v>2451429.4705637945</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f t="shared" si="3"/>
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B4" s="49">
-        <v>486852.17280000012</v>
+        <v>339774</v>
       </c>
       <c r="C4" s="50">
-        <v>774000</v>
+        <v>919534.5</v>
       </c>
       <c r="D4" s="50">
-        <v>1289000</v>
+        <v>1023425.5</v>
       </c>
       <c r="E4" s="50">
-        <v>1498000</v>
+        <v>511055</v>
       </c>
       <c r="F4" s="50">
-        <v>1594000</v>
+        <v>486846</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="0"/>
-        <v>5155000</v>
+        <v>2940861</v>
       </c>
       <c r="H4" s="17">
         <f t="shared" si="1"/>
-        <v>569654.69640525803</v>
+        <v>396349.0117157182</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>4585345.303594742</v>
+        <v>2544511.9882842819</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f t="shared" si="3"/>
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="B5" s="49">
-        <v>492631.71040000021</v>
+        <v>348441</v>
       </c>
       <c r="C5" s="50">
-        <v>792000</v>
+        <v>952752.00000000012</v>
       </c>
       <c r="D5" s="50">
-        <v>1320000</v>
+        <v>1090961.5</v>
       </c>
       <c r="E5" s="50">
-        <v>1477000</v>
+        <v>521287</v>
       </c>
       <c r="F5" s="50">
-        <v>1606000</v>
+        <v>482414.5</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="0"/>
-        <v>5195000</v>
+        <v>3047415</v>
       </c>
       <c r="H5" s="17">
         <f t="shared" si="1"/>
-        <v>576417.20239954337</v>
+        <v>406459.13457544293</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>4618582.7976004565</v>
+        <v>2640955.8654245571</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="3"/>
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="B6" s="49">
-        <v>498212.99</v>
+        <v>356163</v>
       </c>
       <c r="C6" s="50">
-        <v>809000</v>
+        <v>981824.5</v>
       </c>
       <c r="D6" s="50">
-        <v>1352000</v>
+        <v>1158705</v>
       </c>
       <c r="E6" s="50">
-        <v>1457000</v>
+        <v>540270.5</v>
       </c>
       <c r="F6" s="50">
-        <v>1608000</v>
+        <v>471094</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="0"/>
-        <v>5226000</v>
+        <v>3151894</v>
       </c>
       <c r="H6" s="17">
         <f t="shared" si="1"/>
-        <v>582947.73120011389</v>
+        <v>415466.90759064944</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>4643052.2687998861</v>
+        <v>2736427.0924093504</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f t="shared" si="3"/>
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="B7" s="49">
-        <v>503346.44819999998</v>
+        <v>364934</v>
       </c>
       <c r="C7" s="50">
-        <v>826000</v>
+        <v>999278.5</v>
       </c>
       <c r="D7" s="50">
-        <v>1382000</v>
+        <v>1221961.5</v>
       </c>
       <c r="E7" s="50">
-        <v>1443000</v>
+        <v>564893.5</v>
       </c>
       <c r="F7" s="50">
-        <v>1602000</v>
+        <v>456600.5</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="0"/>
-        <v>5253000</v>
+        <v>3242734</v>
       </c>
       <c r="H7" s="17">
         <f t="shared" si="1"/>
-        <v>588954.27432718209</v>
+        <v>425698.34725865984</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>4664045.7256728178</v>
+        <v>2817035.65274134</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="3"/>
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="B8" s="49">
-        <v>508262.75199999998</v>
+        <v>374932</v>
       </c>
       <c r="C8" s="50">
-        <v>842000</v>
+        <v>1003724.5</v>
       </c>
       <c r="D8" s="50">
-        <v>1412000</v>
+        <v>1278873.5</v>
       </c>
       <c r="E8" s="50">
-        <v>1430000</v>
+        <v>597985</v>
       </c>
       <c r="F8" s="50">
-        <v>1587000</v>
+        <v>447872</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" si="0"/>
-        <v>5271000</v>
+        <v>3328455</v>
       </c>
       <c r="H8" s="17">
         <f t="shared" si="1"/>
-        <v>594706.73001104628</v>
+        <v>437361.09196288604</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>4676293.2699889541</v>
+        <v>2891093.908037114</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f t="shared" si="3"/>
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="B9" s="49">
-        <v>512958.06920000009</v>
+        <v>382063</v>
       </c>
       <c r="C9" s="50">
-        <v>859000</v>
+        <v>992948</v>
       </c>
       <c r="D9" s="50">
-        <v>1442000</v>
+        <v>1332921.5</v>
       </c>
       <c r="E9" s="50">
-        <v>1419000</v>
+        <v>642737</v>
       </c>
       <c r="F9" s="50">
-        <v>1565000</v>
+        <v>443614.5</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" si="0"/>
-        <v>5285000</v>
+        <v>3412221</v>
       </c>
       <c r="H9" s="17">
         <f t="shared" si="1"/>
-        <v>600200.61428131582</v>
+        <v>445679.4588848541</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>4684799.3857186846</v>
+        <v>2966541.5411151461</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="3"/>
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="B10" s="49">
-        <v>517428.56760000013</v>
+        <v>389850</v>
       </c>
       <c r="C10" s="50">
-        <v>876000</v>
+        <v>962730</v>
       </c>
       <c r="D10" s="50">
-        <v>1473000</v>
+        <v>1384224</v>
       </c>
       <c r="E10" s="50">
-        <v>1410000</v>
+        <v>697864.5</v>
       </c>
       <c r="F10" s="50">
-        <v>1540000</v>
+        <v>438420.5</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" si="0"/>
-        <v>5299000</v>
+        <v>3483239</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" si="1"/>
-        <v>605431.4431675995</v>
+        <v>454763.05490523914</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>4693568.5568324002</v>
+        <v>3028475.945094761</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f t="shared" si="3"/>
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="B11" s="49">
-        <v>521640.18199999997</v>
+        <v>393953</v>
       </c>
       <c r="C11" s="50">
-        <v>893000</v>
+        <v>920810.49999999988</v>
       </c>
       <c r="D11" s="50">
-        <v>1506000</v>
+        <v>1432116.5</v>
       </c>
       <c r="E11" s="50">
-        <v>1403000</v>
+        <v>760445</v>
       </c>
       <c r="F11" s="50">
-        <v>1516000</v>
+        <v>432251.5</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" si="0"/>
-        <v>5318000</v>
+        <v>3545623.5</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" si="1"/>
-        <v>610359.35775121895</v>
+        <v>459549.23629366083</v>
       </c>
       <c r="I11" s="17">
         <f t="shared" si="2"/>
-        <v>4707640.6422487814</v>
+        <v>3086074.2637063391</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="str">
+      <c r="A12" s="5">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
+        <v>2034</v>
+      </c>
+      <c r="B12" s="49">
+        <v>399765</v>
+      </c>
+      <c r="C12" s="50">
+        <v>877200.49999999988</v>
+      </c>
+      <c r="D12" s="50">
+        <v>1476641.5</v>
+      </c>
+      <c r="E12" s="50">
+        <v>826890</v>
+      </c>
+      <c r="F12" s="50">
+        <v>425198</v>
+      </c>
+      <c r="G12" s="17">
+        <f t="shared" si="0"/>
+        <v>3605930</v>
+      </c>
+      <c r="H12" s="17">
+        <f t="shared" si="1"/>
+        <v>466328.97946439125</v>
+      </c>
+      <c r="I12" s="17">
+        <f t="shared" si="2"/>
+        <v>3139601.0205356088</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="str">
+      <c r="A13" s="5">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
+        <v>2035</v>
+      </c>
+      <c r="B13" s="49">
+        <v>401803</v>
+      </c>
+      <c r="C13" s="50">
+        <v>841554.5</v>
+      </c>
+      <c r="D13" s="50">
+        <v>1512316.5</v>
+      </c>
+      <c r="E13" s="50">
+        <v>894742</v>
+      </c>
+      <c r="F13" s="50">
+        <v>419422</v>
+      </c>
+      <c r="G13" s="17">
+        <f t="shared" si="0"/>
+        <v>3668035</v>
+      </c>
+      <c r="H13" s="17">
+        <f t="shared" si="1"/>
+        <v>468706.32230368035</v>
+      </c>
+      <c r="I13" s="17">
+        <f t="shared" si="2"/>
+        <v>3199328.6776963198</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
@@ -16763,7 +16783,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jdOzr54nnQShzfWJaXO2PK38lJk9KaODFCQ9F2qVFj7hmOB84+44Kt3Zsh8TW3ZEqw2/091FnJlOZJd+2ZiRIg==" saltValue="6N4uAjWvJKwmO+o+a9iJew==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6uz0+xgT9Cy8AQsa/aj+dvv4HHyFBi6lx+MTCPd1Xu2DIhSCyPOB2F6ARzwjA3qAq6b1RAj1h3i7TxX5UDXEQw==" saltValue="H52RU/HukAUQJaAjlSo2Wg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -16842,7 +16862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="104"/>
       <c r="C3" s="8" t="s">
         <v>149</v>
@@ -16864,7 +16884,7 @@
       </c>
       <c r="J3" s="64"/>
     </row>
-    <row r="4" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" s="104"/>
       <c r="C4" s="8" t="s">
         <v>155</v>
@@ -16886,7 +16906,7 @@
       </c>
       <c r="J4" s="64"/>
     </row>
-    <row r="5" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="103" t="s">
         <v>78</v>
       </c>
@@ -16894,9 +16914,7 @@
         <v>150</v>
       </c>
       <c r="D5" s="88">
-        <f>IFERROR((MIN(1,1.56*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.56*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.56)</f>
-        <v>13.599386372649379</v>
+        <v>1.73</v>
       </c>
       <c r="E5" s="88">
         <v>1</v>
@@ -16911,15 +16929,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="104"/>
       <c r="C6" s="8" t="s">
         <v>149</v>
       </c>
       <c r="D6" s="88">
-        <f>IFERROR((MIN(1,1.56*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.56*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.56)</f>
-        <v>13.599386372649379</v>
+        <v>1.73</v>
       </c>
       <c r="E6" s="88">
         <v>1</v>
@@ -16934,7 +16950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" s="104"/>
       <c r="C7" s="8" t="s">
         <v>155</v>
@@ -16955,7 +16971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="103" t="s">
         <v>74</v>
       </c>
@@ -16966,9 +16982,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="88">
-        <f>IFERROR((MIN(1,1.56*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.56*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.56)</f>
-        <v>2.5635913029656501</v>
+        <v>1.73</v>
       </c>
       <c r="F8" s="88">
         <v>1</v>
@@ -16980,7 +16994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="104"/>
       <c r="C9" s="8" t="s">
         <v>149</v>
@@ -16989,9 +17003,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="88">
-        <f>IFERROR((MIN(1,1.56*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.56*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.56)</f>
-        <v>2.5635913029656501</v>
+        <v>1.73</v>
       </c>
       <c r="F9" s="88">
         <v>1</v>
@@ -17003,7 +17015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="104"/>
       <c r="C10" s="8" t="s">
         <v>155</v>
@@ -17024,7 +17036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="103" t="s">
         <v>77</v>
       </c>
@@ -17047,7 +17059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="104"/>
       <c r="C12" s="8" t="s">
         <v>149</v>
@@ -17068,7 +17080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="104"/>
       <c r="C13" s="8" t="s">
         <v>155</v>
@@ -17089,7 +17101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="103" t="s">
         <v>75</v>
       </c>
@@ -17112,7 +17124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="104"/>
       <c r="C15" s="8" t="s">
         <v>149</v>
@@ -17133,7 +17145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="104"/>
       <c r="C16" s="8" t="s">
         <v>155</v>
@@ -17177,7 +17189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D18" s="86"/>
       <c r="E18" s="86"/>
       <c r="F18" s="86"/>
@@ -17210,7 +17222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B20" s="104"/>
       <c r="C20" s="8" t="s">
         <v>149</v>
@@ -17231,7 +17243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B21" s="104"/>
       <c r="C21" s="8" t="s">
         <v>155</v>
@@ -17252,7 +17264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B22" s="103" t="s">
         <v>78</v>
       </c>
@@ -17275,7 +17287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B23" s="104"/>
       <c r="C23" s="8" t="s">
         <v>149</v>
@@ -17296,7 +17308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B24" s="104"/>
       <c r="C24" s="8" t="s">
         <v>155</v>
@@ -17317,7 +17329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B25" s="103" t="s">
         <v>74</v>
       </c>
@@ -17340,7 +17352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B26" s="104"/>
       <c r="C26" s="8" t="s">
         <v>149</v>
@@ -18022,9 +18034,7 @@
         <v>150</v>
       </c>
       <c r="D58" s="88">
-        <f>IFERROR((MIN(1,1.37*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.37*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.37)</f>
-        <v>3.3005928250545504</v>
+        <v>1.35</v>
       </c>
       <c r="E58" s="88">
         <f t="shared" ref="E58:H60" si="1">IF(E5=1,1,E5*0.9)</f>
@@ -18049,9 +18059,7 @@
         <v>149</v>
       </c>
       <c r="D59" s="88">
-        <f>IFERROR((MIN(1,1.37*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.37*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.37)</f>
-        <v>3.3005928250545504</v>
+        <v>1.35</v>
       </c>
       <c r="E59" s="88">
         <f t="shared" si="1"/>
@@ -18108,9 +18116,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="88">
-        <f>IFERROR((MIN(1,1.37*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.37*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.37)</f>
-        <v>1.8479938637880569</v>
+        <v>1.35</v>
       </c>
       <c r="F61" s="88">
         <f t="shared" ref="F61:H63" si="3">IF(F8=1,1,F8*0.9)</f>
@@ -18135,9 +18141,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="88">
-        <f>IFERROR((MIN(1,1.37*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.37*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.37)</f>
-        <v>1.8479938637880569</v>
+        <v>1.35</v>
       </c>
       <c r="F62" s="88">
         <f t="shared" si="3"/>
@@ -19367,9 +19371,7 @@
         <v>150</v>
       </c>
       <c r="D111" s="88">
-        <f>IFERROR((MIN(1,1.77*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.77*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.77)</f>
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="E111" s="88">
         <f t="shared" ref="E111:H113" si="11">IF(E5=1,1,E5*1.05)</f>
@@ -19394,9 +19396,7 @@
         <v>149</v>
       </c>
       <c r="D112" s="88">
-        <f>IFERROR((MIN(1,1.77*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.77*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.77)</f>
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="E112" s="88">
         <f t="shared" si="11"/>
@@ -19453,9 +19453,7 @@
         <v>1</v>
       </c>
       <c r="E114" s="88">
-        <f>IFERROR((MIN(1,1.77*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.77*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.77)</f>
-        <v>3.8335184418186232</v>
+        <v>2.11</v>
       </c>
       <c r="F114" s="88">
         <f t="shared" ref="F114:H116" si="13">IF(F8=1,1,F8*1.05)</f>
@@ -19480,9 +19478,7 @@
         <v>1</v>
       </c>
       <c r="E115" s="88">
-        <f>IFERROR((MIN(1,1.77*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.77*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.77)</f>
-        <v>3.8335184418186232</v>
+        <v>2.11</v>
       </c>
       <c r="F115" s="88">
         <f t="shared" si="13"/>
@@ -20584,7 +20580,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="G0KpzLSb7NY6Xfwen8Zn3fxNadBLKVrcr8GiY46BykkW9p9iwq427RL4r6kiQ2SGX0PCAxMG7+kSQLzCVXiReg==" saltValue="CvihE3WKM5VHxjkuZhOFrA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HPr4nJ1ikylNk8T/X/HZ/lG78ALO9iobnw6zmITeX1vXNEHceau7bsXryJxuLoCloJcqCjDayKLQUYpxTSZ/Fg==" saltValue="B+oA5Dayf/+lyA1KcnC0yQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B148:B150"/>
@@ -21846,7 +21842,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dA71BMiWao8IsNdFcn/nhyzbY/aZJveQAx6x7FxC2+YZHtPquNjJplA7+oQlL+/j5SdV6iz+XD8PSbvzPH8xMA==" saltValue="2oCY8a6bQ5juOIT10XDzcA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="VMLqLnl7cn1/xR4MiZQoka440fpHxdJ2PlQK4Gb97+QiIpVa++4/+KPRXZmfu+p7gvFGsPOgAbiB2oqn/FX/TQ==" saltValue="WgUXV8Zhqpj+8rs3qFkkeA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -29981,7 +29977,7 @@
       <c r="I328" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="oRZMimmTgJ4iZ73KJrllNj+vhid34JJf7EQYHsHdrpO3XGcGDh+1XS7i0g8p3V1Bwtk+aq6NVvBqEdV0zoPGoA==" saltValue="pVnKLx1yitUAUPIpd2YPmA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="UeVrB9xJ5a5xicXfOgqWt0VZcr1StjPFdGakKsVqU/z14mLUkn5Io3HqMAEZ7RZuD4cwYEk7OfnIFsG8ib62XQ==" saltValue="6SI4LP+lVfbm+EIprKY58Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -30090,13 +30086,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$E$4),0.64, (0.64*SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-0.64*SUM('Distribución estado nutricional'!$E$4:$E$5)))
-/ (SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-SUM('Distribución estado nutricional'!$E$4:$E$5))))</f>
-        <v>0.59481595868259551</v>
+        <v>0.89</v>
       </c>
       <c r="F6" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$F$4),0.64, (0.64*SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-0.64*SUM('Distribución estado nutricional'!$F$4:$F$5)))/ (SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-SUM('Distribución estado nutricional'!$F$4:$F$5))))</f>
-        <v>0.55141449272276066</v>
+        <v>0.89</v>
       </c>
       <c r="G6" s="90">
         <v>1</v>
@@ -30113,12 +30106,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$E$4),0.88, (0.88*SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-0.88*SUM('Distribución estado nutricional'!$E$4:$E$5)))/ (SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-SUM('Distribución estado nutricional'!$E$4:$E$5))))</f>
-        <v>0.85826778381928515</v>
+        <v>0.88</v>
       </c>
       <c r="F7" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$F$4),0.88, (0.88*SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-0.88*SUM('Distribución estado nutricional'!$F$4:$F$5)))/ (SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-SUM('Distribución estado nutricional'!$F$4:$F$5))))</f>
-        <v>0.83527085729295292</v>
+        <v>0.88</v>
       </c>
       <c r="G7" s="90">
         <v>1</v>
@@ -30135,12 +30126,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$E$4),0.88, (0.88*SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-0.88*SUM('Distribución estado nutricional'!$E$4:$E$5)))/ (SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-SUM('Distribución estado nutricional'!$E$4:$E$5))))</f>
-        <v>0.85826778381928515</v>
+        <v>0.88</v>
       </c>
       <c r="F8" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$F$4),0.88, (0.88*SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-0.88*SUM('Distribución estado nutricional'!$F$4:$F$5)))/ (SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-SUM('Distribución estado nutricional'!$F$4:$F$5))))</f>
-        <v>0.83527085729295292</v>
+        <v>0.88</v>
       </c>
       <c r="G8" s="90">
         <v>1</v>
@@ -30418,12 +30407,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.44, (0.44*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.44*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.39350193706075004</v>
+        <f>E6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="F29" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.44, (0.44*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.44*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.35202755124466439</v>
+        <f>F6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="G29" s="90">
         <f>IF(G6=1,1,G6*0.9)</f>
@@ -30443,12 +30432,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.85, (0.85*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.85*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.8239218232405956</v>
+        <v>0.85</v>
       </c>
       <c r="F30" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.85, (0.85*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.85*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.79667228591718775</v>
+        <v>0.85</v>
       </c>
       <c r="G30" s="90">
         <f>IF(G7=1,1,G7*0.9)</f>
@@ -30468,12 +30455,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.85, (0.85*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.85*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.8239218232405956</v>
+        <v>0.85</v>
       </c>
       <c r="F31" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.85, (0.85*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.85*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.79667228591718775</v>
+        <v>0.85</v>
       </c>
       <c r="G31" s="90">
         <f>IF(G8=1,1,G8*0.9)</f>
@@ -30530,12 +30515,10 @@
         <v>303</v>
       </c>
       <c r="C35" s="90">
-        <f>C12*0.9</f>
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="D35" s="90">
-        <f>D12*0.9</f>
-        <v>1.2509999999999999</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E35" s="90">
         <v>1</v>
@@ -30795,12 +30778,12 @@
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.92, (0.92*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.92*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.90472758286236654</v>
+        <f>E6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="F52" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.92, (0.92*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.92*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.88828784851119058</v>
+        <f>F6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="G52" s="90">
         <f>IF(G6=1,1,G6*1.1)</f>
@@ -30820,12 +30803,10 @@
         <v>1</v>
       </c>
       <c r="E53" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.91, (0.91*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.91*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.8930404777908173</v>
+        <v>0.91</v>
       </c>
       <c r="F53" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.91, (0.91*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.91*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.87486300935825312</v>
+        <v>0.91</v>
       </c>
       <c r="G53" s="90">
         <f>IF(G7=1,1,G7*1.1)</f>
@@ -30845,12 +30826,10 @@
         <v>1</v>
       </c>
       <c r="E54" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.91, (0.91*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.91*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.8930404777908173</v>
+        <v>0.91</v>
       </c>
       <c r="F54" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.91, (0.91*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.91*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.87486300935825312</v>
+        <v>0.91</v>
       </c>
       <c r="G54" s="90">
         <f>IF(G8=1,1,G8*1.1)</f>
@@ -30907,12 +30886,10 @@
         <v>304</v>
       </c>
       <c r="C58" s="90">
-        <f>C12*1.1</f>
-        <v>1.6500000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="D58" s="90">
-        <f>D12*1.1</f>
-        <v>1.5289999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="E58" s="90">
         <v>1</v>
@@ -31068,7 +31045,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bkDgx1mMOF9FBhXEVepwsqZBESsPyDn8m2w1/vmmpAVyGry2aAvnf/GJZySl2smLJC9g1xlftR60X5xOkutOYA==" saltValue="51cLCZdRgAPgcvET0amu/w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="s1sWKL4sSdlEsdkW1dCziNAT+5GTrOqFpZrHt6W79IO/g+62/30f7VcE63iS60ZrOuVEOkptVGcNsiWle+lBew==" saltValue="vaRb5csksxlVa4aGp4fKDQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -31889,7 +31866,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OqKPGnfJrcw7VfQGJ+N7a9NFbpZ4U/2gSHjM+06J7ARAXdV+M0HooIOf+ncRgnpMkJ/p0Ekqu6zpnJSAHCGLFg==" saltValue="R+b0MCjzvBu2T2i6lgQrkA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="R+ZMTDIJFGSbsymWfI3zmidCGhmj3Xq/K8/IIHMJizi21wK+2MqbOXDLzgq3jPhEatSHsqtA+i2Qa2NWg+Gycg==" saltValue="vS1gbYDepe7kla718OVRGw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -31964,7 +31941,7 @@
         <v>169</v>
       </c>
       <c r="C3" s="90">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="D3" s="90">
         <v>0.53</v>
@@ -32299,16 +32276,16 @@
         <v>1</v>
       </c>
       <c r="L10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="M10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="N10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="O10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -32475,15 +32452,19 @@
         <v>1</v>
       </c>
       <c r="L14" s="90">
+        <f>L8</f>
         <v>0.51</v>
       </c>
       <c r="M14" s="90">
+        <f>M8</f>
         <v>0.51</v>
       </c>
       <c r="N14" s="90">
+        <f>N8</f>
         <v>0.51</v>
       </c>
       <c r="O14" s="90">
+        <f>O8</f>
         <v>0.51</v>
       </c>
     </row>
@@ -32592,59 +32573,37 @@
         <v>1</v>
       </c>
       <c r="E19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.72,(0.72*'Distribución estado nutricional'!E$14/(1-0.72*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.43079783006287031</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.72,(0.72*'Distribución estado nutricional'!F$14/(1-0.72*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.47383392432005694</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.72,(0.72*'Distribución estado nutricional'!G$14/(1-0.72*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.47383392432005694</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.72,(0.72*'Distribución estado nutricional'!H$14/(1-0.72*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.61106789643293691</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.72,(0.72*'Distribución estado nutricional'!I$14/(1-0.72*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.61106789643293691</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.72,(0.72*'Distribución estado nutricional'!J$14/(1-0.72*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.61106789643293691</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.72,(0.72*'Distribución estado nutricional'!K$14/(1-0.72*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.61106789643293691</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.72,(0.72*'Distribución estado nutricional'!L$14/(1-0.72*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.63099630996309952</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.72,(0.72*'Distribución estado nutricional'!M$14/(1-0.72*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.63099630996309952</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.72,(0.72*'Distribución estado nutricional'!N$14/(1-0.72*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.63099630996309952</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.72,(0.72*'Distribución estado nutricional'!O$14/(1-0.72*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.63099630996309952</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -32658,37 +32617,48 @@
         <v>1</v>
       </c>
       <c r="E20" s="90">
-        <v>1</v>
+        <f t="shared" ref="E20:O20" si="0">E19</f>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -32702,59 +32672,37 @@
         <v>1</v>
       </c>
       <c r="E21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.8,(0.8*'Distribución estado nutricional'!E$14/(1-0.8*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.54071862000244175</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.8,(0.8*'Distribución estado nutricional'!F$14/(1-0.8*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.58347928311998087</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.8,(0.8*'Distribución estado nutricional'!G$14/(1-0.8*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.58347928311998087</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.8,(0.8*'Distribución estado nutricional'!H$14/(1-0.8*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.70963995354239262</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.8,(0.8*'Distribución estado nutricional'!I$14/(1-0.8*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.70963995354239262</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.8,(0.8*'Distribución estado nutricional'!J$14/(1-0.8*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.70963995354239262</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.8,(0.8*'Distribución estado nutricional'!K$14/(1-0.8*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.70963995354239262</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.8,(0.8*'Distribución estado nutricional'!L$14/(1-0.8*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.72677595628415304</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.8,(0.8*'Distribución estado nutricional'!M$14/(1-0.8*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.72677595628415304</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.8,(0.8*'Distribución estado nutricional'!N$14/(1-0.8*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.72677595628415304</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O21" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.8,(0.8*'Distribución estado nutricional'!O$14/(1-0.8*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.72677595628415304</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -32815,53 +32763,53 @@
         <v>169</v>
       </c>
       <c r="C26" s="90">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="D26" s="90">
         <v>0.4</v>
       </c>
       <c r="E26" s="90">
-        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="1">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -32870,23 +32818,23 @@
         <v>174</v>
       </c>
       <c r="C27" s="90">
-        <f t="shared" ref="C27:G33" si="1">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:G33" si="2">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H27" s="90">
@@ -32902,19 +32850,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="90">
-        <f t="shared" ref="L27:O30" si="2">IF(L4=1,1,L4*0.9)</f>
+        <f t="shared" ref="L27:O30" si="3">IF(L4=1,1,L4*0.9)</f>
         <v>1</v>
       </c>
       <c r="M27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -32923,23 +32871,23 @@
         <v>175</v>
       </c>
       <c r="C28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H28" s="90">
@@ -32955,19 +32903,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -32976,23 +32924,23 @@
         <v>176</v>
       </c>
       <c r="C29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H29" s="90">
@@ -33008,19 +32956,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -33029,23 +32977,23 @@
         <v>177</v>
       </c>
       <c r="C30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H30" s="90">
@@ -33061,19 +33009,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -33082,39 +33030,39 @@
         <v>178</v>
       </c>
       <c r="C31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H31" s="90">
-        <f t="shared" ref="H31:K34" si="3">IF(H8=1,1,H8*0.9)</f>
+        <f t="shared" ref="H31:K34" si="4">IF(H8=1,1,H8*0.9)</f>
         <v>1</v>
       </c>
       <c r="I31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L31" s="90">
@@ -33135,39 +33083,39 @@
         <v>179</v>
       </c>
       <c r="C32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L32" s="90">
@@ -33188,39 +33136,39 @@
         <v>180</v>
       </c>
       <c r="C33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L33" s="90">
@@ -33258,19 +33206,19 @@
         <v>1</v>
       </c>
       <c r="H34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L34" s="90">
@@ -33339,11 +33287,11 @@
         <v>190</v>
       </c>
       <c r="C36" s="90">
-        <f t="shared" ref="C36:D38" si="4">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:D38" si="5">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E36" s="90">
@@ -33356,35 +33304,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="90">
-        <f t="shared" ref="H36:O36" si="5">IF(H13=1,1,H13*0.9)</f>
+        <f t="shared" ref="H36:O36" si="6">IF(H13=1,1,H13*0.9)</f>
         <v>1</v>
       </c>
       <c r="I36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -33393,56 +33341,52 @@
         <v>191</v>
       </c>
       <c r="C37" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D37" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E37" s="90">
-        <f t="shared" ref="E37:K37" si="6">IF(E14=1,1,E14*0.9)</f>
+        <f t="shared" ref="E37:K37" si="7">IF(E14=1,1,E14*0.9)</f>
         <v>1</v>
       </c>
       <c r="F37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L37" s="90">
-        <f>L32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="M37" s="90">
-        <f>M32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="N37" s="90">
-        <f>N32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="O37" s="90">
-        <f>O32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -33450,11 +33394,11 @@
         <v>204</v>
       </c>
       <c r="C38" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D38" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E38" s="90">
@@ -33464,39 +33408,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="90">
-        <f t="shared" ref="G38:O38" si="7">IF(G15=1,1,G15*0.9)</f>
+        <f t="shared" ref="G38:O38" si="8">IF(G15=1,1,G15*0.9)</f>
         <v>1</v>
       </c>
       <c r="H38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -33511,55 +33455,55 @@
         <v>171</v>
       </c>
       <c r="C41" s="90">
-        <f t="shared" ref="C41:O41" si="8">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:O41" si="9">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="I41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="L41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="M41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="O41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -33568,67 +33512,45 @@
         <v>172</v>
       </c>
       <c r="C42" s="90">
-        <f t="shared" ref="C42:D44" si="9">IF(C19=1,1,C19*0.9)</f>
+        <f t="shared" ref="C42:D44" si="10">IF(C19=1,1,C19*0.9)</f>
         <v>1</v>
       </c>
       <c r="D42" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.54,(0.54*'Distribución estado nutricional'!E$14/(1-0.54*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.25679081750843147</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.54,(0.54*'Distribución estado nutricional'!F$14/(1-0.54*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.29134122381918504</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.54,(0.54*'Distribución estado nutricional'!G$14/(1-0.54*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.29134122381918504</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.54,(0.54*'Distribución estado nutricional'!H$14/(1-0.54*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.41767729194622383</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.54,(0.54*'Distribución estado nutricional'!I$14/(1-0.54*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.41767729194622383</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.54,(0.54*'Distribución estado nutricional'!J$14/(1-0.54*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.41767729194622383</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.54,(0.54*'Distribución estado nutricional'!K$14/(1-0.54*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.41767729194622383</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.54,(0.54*'Distribución estado nutricional'!L$14/(1-0.54*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.43840800879013564</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.54,(0.54*'Distribución estado nutricional'!M$14/(1-0.54*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.43840800879013564</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.54,(0.54*'Distribución estado nutricional'!N$14/(1-0.54*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.43840800879013564</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O42" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.54,(0.54*'Distribución estado nutricional'!O$14/(1-0.54*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.43840800879013564</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -33636,56 +33558,56 @@
         <v>173</v>
       </c>
       <c r="C43" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D43" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E43" s="90">
-        <f t="shared" ref="E43:O43" si="10">IF(E20=1,1,E20*0.9)</f>
-        <v>1</v>
+        <f t="shared" ref="E43:O43" si="11">IF(E20=1,1,E20*0.9)</f>
+        <v>0.87839999999999996</v>
       </c>
       <c r="F43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="G43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="H43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="I43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="J43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="K43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="L43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="M43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="N43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="O43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -33693,67 +33615,45 @@
         <v>181</v>
       </c>
       <c r="C44" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D44" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.7,(0.7*'Distribución estado nutricional'!E$14/(1-0.7*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.40714981398050276</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.7,(0.7*'Distribución estado nutricional'!F$14/(1-0.7*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.44968988725380282</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.7,(0.7*'Distribución estado nutricional'!G$14/(1-0.7*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.44968988725380282</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.7,(0.7*'Distribución estado nutricional'!H$14/(1-0.7*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.58774220145664413</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.7,(0.7*'Distribución estado nutricional'!I$14/(1-0.7*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.58774220145664413</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.7,(0.7*'Distribución estado nutricional'!J$14/(1-0.7*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.58774220145664413</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.7,(0.7*'Distribución estado nutricional'!K$14/(1-0.7*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.58774220145664413</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.7,(0.7*'Distribución estado nutricional'!L$14/(1-0.7*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.60809928151534931</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.7,(0.7*'Distribución estado nutricional'!M$14/(1-0.7*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.60809928151534931</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.7,(0.7*'Distribución estado nutricional'!N$14/(1-0.7*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.60809928151534931</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O44" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.7,(0.7*'Distribución estado nutricional'!O$14/(1-0.7*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.60809928151534931</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -33814,53 +33714,53 @@
         <v>169</v>
       </c>
       <c r="C49" s="90">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="D49" s="90">
         <v>0.7</v>
       </c>
       <c r="E49" s="90">
-        <f t="shared" ref="E49:O49" si="11">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="12">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="I49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="M49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="N49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="O49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -33869,23 +33769,23 @@
         <v>174</v>
       </c>
       <c r="C50" s="90">
-        <f t="shared" ref="C50:G56" si="12">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:G56" si="13">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H50" s="90">
@@ -33901,19 +33801,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="90">
-        <f t="shared" ref="L50:O53" si="13">IF(L4=1,1,L4*1.05)</f>
+        <f t="shared" ref="L50:O53" si="14">IF(L4=1,1,L4*1.05)</f>
         <v>1</v>
       </c>
       <c r="M50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -33922,23 +33822,23 @@
         <v>175</v>
       </c>
       <c r="C51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H51" s="90">
@@ -33954,19 +33854,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -33975,23 +33875,23 @@
         <v>176</v>
       </c>
       <c r="C52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H52" s="90">
@@ -34007,19 +33907,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -34028,23 +33928,23 @@
         <v>177</v>
       </c>
       <c r="C53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H53" s="90">
@@ -34060,19 +33960,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -34081,39 +33981,39 @@
         <v>178</v>
       </c>
       <c r="C54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H54" s="90">
-        <f t="shared" ref="H54:K57" si="14">IF(H8=1,1,H8*1.05)</f>
+        <f t="shared" ref="H54:K57" si="15">IF(H8=1,1,H8*1.05)</f>
         <v>1</v>
       </c>
       <c r="I54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L54" s="90">
@@ -34134,39 +34034,39 @@
         <v>179</v>
       </c>
       <c r="C55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L55" s="90">
@@ -34187,52 +34087,52 @@
         <v>180</v>
       </c>
       <c r="C56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="M56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="N56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="O56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -34258,19 +34158,19 @@
         <v>1</v>
       </c>
       <c r="H57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L57" s="90">
@@ -34339,11 +34239,11 @@
         <v>190</v>
       </c>
       <c r="C59" s="90">
-        <f t="shared" ref="C59:D61" si="15">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:D61" si="16">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E59" s="90">
@@ -34356,35 +34256,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="90">
-        <f t="shared" ref="H59:O59" si="16">IF(H13=1,1,H13*1.05)</f>
+        <f t="shared" ref="H59:O59" si="17">IF(H13=1,1,H13*1.05)</f>
         <v>1</v>
       </c>
       <c r="I59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="J59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="K59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -34393,56 +34293,52 @@
         <v>191</v>
       </c>
       <c r="C60" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="D60" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E60" s="90">
-        <f t="shared" ref="E60:K60" si="17">IF(E14=1,1,E14*1.05)</f>
+        <f t="shared" ref="E60:K60" si="18">IF(E14=1,1,E14*1.05)</f>
         <v>1</v>
       </c>
       <c r="F60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="I60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="J60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="K60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="L60" s="90">
-        <f>L54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M60" s="90">
-        <f>M54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N60" s="90">
-        <f>N54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O60" s="90">
-        <f>O54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -34450,11 +34346,11 @@
         <v>204</v>
       </c>
       <c r="C61" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="D61" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E61" s="90">
@@ -34464,39 +34360,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="90">
-        <f t="shared" ref="G61:O61" si="18">IF(G15=1,1,G15*1.05)</f>
+        <f t="shared" ref="G61:O61" si="19">IF(G15=1,1,G15*1.05)</f>
         <v>1</v>
       </c>
       <c r="H61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="I61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="J61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="K61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="L61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="N61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="O61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
@@ -34511,55 +34407,55 @@
         <v>171</v>
       </c>
       <c r="C64" s="90">
-        <f t="shared" ref="C64:O64" si="19">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:O64" si="20">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="I64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="J64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="K64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="L64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="M64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="N64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="O64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -34568,67 +34464,45 @@
         <v>172</v>
       </c>
       <c r="C65" s="90">
-        <f t="shared" ref="C65:D67" si="20">IF(C19=1,1,C19*1.05)</f>
+        <f t="shared" ref="C65:D67" si="21">IF(C19=1,1,C19*1.05)</f>
         <v>1</v>
       </c>
       <c r="D65" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.97,(0.97*'Distribución estado nutricional'!E$14/(1-0.97*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.90491246361843825</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.97,(0.97*'Distribución estado nutricional'!F$14/(1-0.97*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.91885398765538573</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.97,(0.97*'Distribución estado nutricional'!G$14/(1-0.97*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.91885398765538573</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.97,(0.97*'Distribución estado nutricional'!H$14/(1-0.97*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.95182038640050093</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.97,(0.97*'Distribución estado nutricional'!I$14/(1-0.97*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.95182038640050093</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.97,(0.97*'Distribución estado nutricional'!J$14/(1-0.97*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.95182038640050093</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.97,(0.97*'Distribución estado nutricional'!K$14/(1-0.97*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.95182038640050093</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.97,(0.97*'Distribución estado nutricional'!L$14/(1-0.97*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.95555884749277842</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.97,(0.97*'Distribución estado nutricional'!M$14/(1-0.97*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.95555884749277842</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.97,(0.97*'Distribución estado nutricional'!N$14/(1-0.97*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.95555884749277842</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O65" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.97,(0.97*'Distribución estado nutricional'!O$14/(1-0.97*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.95555884749277842</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.25">
@@ -34636,56 +34510,56 @@
         <v>173</v>
       </c>
       <c r="C66" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="D66" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E66" s="90">
-        <f t="shared" ref="E66:O66" si="21">IF(E20=1,1,E20*1.05)</f>
-        <v>1</v>
+        <f t="shared" ref="E66:O66" si="22">IF(E20=1,1,E20*1.05)</f>
+        <v>1.0247999999999999</v>
       </c>
       <c r="F66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="G66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="H66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="I66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="J66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="K66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="L66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="M66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="N66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="O66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
@@ -34693,71 +34567,49 @@
         <v>181</v>
       </c>
       <c r="C67" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="D67" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.92,(0.92*'Distribución estado nutricional'!E$14/(1-0.92*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.7719383419291137</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.92,(0.92*'Distribución estado nutricional'!F$14/(1-0.92*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.80109072993688135</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.92,(0.92*'Distribución estado nutricional'!G$14/(1-0.92*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.80109072993688135</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.92,(0.92*'Distribución estado nutricional'!H$14/(1-0.92*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.87541269544633404</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.92,(0.92*'Distribución estado nutricional'!I$14/(1-0.92*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.87541269544633404</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.92,(0.92*'Distribución estado nutricional'!J$14/(1-0.92*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.87541269544633404</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.92,(0.92*'Distribución estado nutricional'!K$14/(1-0.92*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.87541269544633404</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.92,(0.92*'Distribución estado nutricional'!L$14/(1-0.92*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.88435964151488877</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.92,(0.92*'Distribución estado nutricional'!M$14/(1-0.92*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.88435964151488877</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.92,(0.92*'Distribución estado nutricional'!N$14/(1-0.92*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.88435964151488877</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O67" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.92,(0.92*'Distribución estado nutricional'!O$14/(1-0.92*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.88435964151488877</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="TqFzYyIdC+yjhrIV4g2H/Fv2YqY17WD9wybtYDXabVEj6x5n8AjuW+L3j7kmTD/bs1U3ngvIF75mSosGZdDfMw==" saltValue="bM+wDx7eXt07eOdEkca2tQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uYMTuUDUvsX90r1XwZbiNvfs6miIk1NeZGND6s/foG24Xhfz9TheQuFzqfL9mEr5rfUC86NysA9bUdE+HP0v0Q==" saltValue="nBWkKrncyHdD8nhoo+IBXQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -34803,7 +34655,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>164</v>
       </c>
@@ -34811,24 +34663,20 @@
         <v>1</v>
       </c>
       <c r="D3" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$11),(1/1.33),((1/1.33)*'Distribución estado nutricional'!D$11/(1-(1/1.33)*'Distribución estado nutricional'!D$11))
-/ ('Distribución estado nutricional'!D$11/(1-'Distribución estado nutricional'!D$11)))</f>
-        <v>0.73450846895024891</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="E3" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$11),(1/1.33),((1/1.33)*'Distribución estado nutricional'!E$11/(1-(1/1.33)*'Distribución estado nutricional'!E$11))
-/ ('Distribución estado nutricional'!E$11/(1-'Distribución estado nutricional'!E$11)))</f>
-        <v>0.72837998741222798</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="F3" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$11),(1/1.33),((1/1.33)*'Distribución estado nutricional'!F$11/(1-(1/1.33)*'Distribución estado nutricional'!F$11))
-/ ('Distribución estado nutricional'!F$11/(1-'Distribución estado nutricional'!F$11)))</f>
-        <v>0.73231123381141583</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="G3" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$11),(1/1.33),((1/1.33)*'Distribución estado nutricional'!G$11/(1-(1/1.33)*'Distribución estado nutricional'!G$11))
-/ ('Distribución estado nutricional'!G$11/(1-'Distribución estado nutricional'!G$11)))</f>
-        <v>0.73296537404992301</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34842,7 +34690,7 @@
       <c r="F4" s="83"/>
       <c r="G4" s="83"/>
     </row>
-    <row r="5" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>162</v>
       </c>
@@ -34850,24 +34698,20 @@
         <v>1</v>
       </c>
       <c r="D5" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$10),(1/1.33),((1/1.33)*'Distribución estado nutricional'!D$10/(1-(1/1.33)*'Distribución estado nutricional'!D$10))
-/ ('Distribución estado nutricional'!D$10/(1-'Distribución estado nutricional'!D$10)))</f>
-        <v>0.72906382152921545</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="E5" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$10),(1/1.33),((1/1.33)*'Distribución estado nutricional'!E$10/(1-(1/1.33)*'Distribución estado nutricional'!E$10))
-/ ('Distribución estado nutricional'!E$10/(1-'Distribución estado nutricional'!E$10)))</f>
-        <v>0.71891334870794765</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="F5" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$10),(1/1.33),((1/1.33)*'Distribución estado nutricional'!F$10/(1-(1/1.33)*'Distribución estado nutricional'!F$10))
-/ ('Distribución estado nutricional'!F$10/(1-'Distribución estado nutricional'!F$10)))</f>
-        <v>0.72544552382944072</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="G5" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$10),(1/1.33),((1/1.33)*'Distribución estado nutricional'!G$10/(1-(1/1.33)*'Distribución estado nutricional'!G$10))
-/ ('Distribución estado nutricional'!G$10/(1-'Distribución estado nutricional'!G$10)))</f>
-        <v>0.726445521091998</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34899,7 +34743,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>164</v>
       </c>
@@ -34907,24 +34751,20 @@
         <v>1</v>
       </c>
       <c r="D10" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$11),(1/1.54),((1/1.54)*'Distribución estado nutricional'!D$11/(1-(1/1.54)*'Distribución estado nutricional'!D$11))
-/ ('Distribución estado nutricional'!D$11/(1-'Distribución estado nutricional'!D$11)))</f>
-        <v>0.6283493726849767</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="E10" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$11),(1/1.54),((1/1.54)*'Distribución estado nutricional'!E$11/(1-(1/1.54)*'Distribución estado nutricional'!E$11))
-/ ('Distribución estado nutricional'!E$11/(1-'Distribución estado nutricional'!E$11)))</f>
-        <v>0.62103469924925681</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="F10" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$11),(1/1.54),((1/1.54)*'Distribución estado nutricional'!F$11/(1-(1/1.54)*'Distribución estado nutricional'!F$11))
-/ ('Distribución estado nutricional'!F$11/(1-'Distribución estado nutricional'!F$11)))</f>
-        <v>0.62572124815068297</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G10" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$11),(1/1.54),((1/1.54)*'Distribución estado nutricional'!G$11/(1-(1/1.54)*'Distribución estado nutricional'!G$11))
-/ ('Distribución estado nutricional'!G$11/(1-'Distribución estado nutricional'!G$11)))</f>
-        <v>0.62650301202230407</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34938,7 +34778,7 @@
       <c r="F11" s="83"/>
       <c r="G11" s="83"/>
     </row>
-    <row r="12" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>162</v>
       </c>
@@ -34946,24 +34786,20 @@
         <v>1</v>
       </c>
       <c r="D12" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$10),(1/1.54),((1/1.54)*'Distribución estado nutricional'!D$10/(1-(1/1.54)*'Distribución estado nutricional'!D$10))
-/ ('Distribución estado nutricional'!D$10/(1-'Distribución estado nutricional'!D$10)))</f>
-        <v>0.62184848011692317</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="E12" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$10),(1/1.54),((1/1.54)*'Distribución estado nutricional'!E$10/(1-(1/1.54)*'Distribución estado nutricional'!E$10))
-/ ('Distribución estado nutricional'!E$10/(1-'Distribución estado nutricional'!E$10)))</f>
-        <v>0.60983087355252086</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="F12" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$10),(1/1.54),((1/1.54)*'Distribución estado nutricional'!F$10/(1-(1/1.54)*'Distribución estado nutricional'!F$10))
-/ ('Distribución estado nutricional'!F$10/(1-'Distribución estado nutricional'!F$10)))</f>
-        <v>0.61754945401216199</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G12" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$10),(1/1.54),((1/1.54)*'Distribución estado nutricional'!G$10/(1-(1/1.54)*'Distribución estado nutricional'!G$10))
-/ ('Distribución estado nutricional'!G$10/(1-'Distribución estado nutricional'!G$10)))</f>
-        <v>0.6187358996181741</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34995,7 +34831,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
         <v>164</v>
       </c>
@@ -35003,24 +34839,20 @@
         <v>1</v>
       </c>
       <c r="D17" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$11),(1/1.16),((1/1.16)*'Distribución estado nutricional'!D$11/(1-(1/1.16)*'Distribución estado nutricional'!D$11))
-/ ('Distribución estado nutricional'!D$11/(1-'Distribución estado nutricional'!D$11)))</f>
-        <v>0.85088224148312031</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="E17" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$11),(1/1.16),((1/1.16)*'Distribución estado nutricional'!E$11/(1-(1/1.16)*'Distribución estado nutricional'!E$11))
-/ ('Distribución estado nutricional'!E$11/(1-'Distribución estado nutricional'!E$11)))</f>
-        <v>0.84688007191163805</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="F17" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$11),(1/1.16),((1/1.16)*'Distribución estado nutricional'!F$11/(1-(1/1.16)*'Distribución estado nutricional'!F$11))
-/ ('Distribución estado nutricional'!F$11/(1-'Distribución estado nutricional'!F$11)))</f>
-        <v>0.84945072048325976</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="G17" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$11),(1/1.16),((1/1.16)*'Distribución estado nutricional'!G$11/(1-(1/1.16)*'Distribución estado nutricional'!G$11))
-/ ('Distribución estado nutricional'!G$11/(1-'Distribución estado nutricional'!G$11)))</f>
-        <v>0.84987729230860742</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -35034,7 +34866,7 @@
       <c r="F18" s="83"/>
       <c r="G18" s="83"/>
     </row>
-    <row r="19" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>162</v>
       </c>
@@ -35042,28 +34874,24 @@
         <v>1</v>
       </c>
       <c r="D19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$10),(1/1.16),((1/1.16)*'Distribución estado nutricional'!D$10/(1-(1/1.16)*'Distribución estado nutricional'!D$10))
-/ ('Distribución estado nutricional'!D$10/(1-'Distribución estado nutricional'!D$10)))</f>
-        <v>0.84732810158440031</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="E19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$10),(1/1.16),((1/1.16)*'Distribución estado nutricional'!E$10/(1-(1/1.16)*'Distribución estado nutricional'!E$10))
-/ ('Distribución estado nutricional'!E$10/(1-'Distribución estado nutricional'!E$10)))</f>
-        <v>0.84063986218246922</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="F19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$10),(1/1.16),((1/1.16)*'Distribución estado nutricional'!F$10/(1-(1/1.16)*'Distribución estado nutricional'!F$10))
-/ ('Distribución estado nutricional'!F$10/(1-'Distribución estado nutricional'!F$10)))</f>
-        <v>0.84495331650972483</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="G19" s="90">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$10),(1/1.16),((1/1.16)*'Distribución estado nutricional'!G$10/(1-(1/1.16)*'Distribución estado nutricional'!G$10))
-/ ('Distribución estado nutricional'!G$10/(1-'Distribución estado nutricional'!G$10)))</f>
-        <v>0.84561067180888705</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ClxIM51cKmoZ39DV+WNENufl2tVYnVBjQVY8nLC/aTNQzGRTQqdwMjq7yYUMww8PoZrWcFrNJ5zQHi5hUvPbOQ==" saltValue="uobt1AKCSdUI0SntdfTbuw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="r7Zm/UsKxA28Q3TSBdl3YvX6Rr0Tyt5gYoNO+76H8p0ZosF/FUobRQlxER689srrL0OOHy0Ze53baWs3+XVscA==" saltValue="3eTRloZcE4Fc/h+J5aO66Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -35116,7 +34944,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>196</v>
       </c>
@@ -35142,7 +34970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C3" s="5" t="s">
         <v>339</v>
       </c>
@@ -35162,7 +34990,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C4" s="5" t="s">
         <v>338</v>
       </c>
@@ -35182,7 +35010,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>193</v>
       </c>
@@ -35208,7 +35036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C6" s="5" t="s">
         <v>338</v>
       </c>
@@ -35228,7 +35056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
@@ -35251,7 +35079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C8" s="5" t="s">
         <v>338</v>
       </c>
@@ -35271,7 +35099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>184</v>
       </c>
@@ -35297,7 +35125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
         <v>338</v>
       </c>
@@ -35317,7 +35145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
@@ -35340,7 +35168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
         <v>338</v>
       </c>
@@ -35360,7 +35188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>204</v>
       </c>
@@ -35386,7 +35214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
         <v>338</v>
       </c>
@@ -35406,7 +35234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -35429,7 +35257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
         <v>338</v>
       </c>
@@ -35449,7 +35277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>167</v>
       </c>
@@ -35475,7 +35303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C18" s="5" t="s">
         <v>338</v>
       </c>
@@ -35495,7 +35323,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
@@ -35518,7 +35346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
         <v>338</v>
       </c>
@@ -35538,7 +35366,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>173</v>
       </c>
@@ -35564,7 +35392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
         <v>339</v>
       </c>
@@ -35584,7 +35412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>171</v>
       </c>
@@ -35610,7 +35438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C24" s="5" t="s">
         <v>339</v>
       </c>
@@ -35630,7 +35458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>172</v>
       </c>
@@ -35656,7 +35484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C26" s="5" t="s">
         <v>339</v>
       </c>
@@ -35676,7 +35504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>200</v>
       </c>
@@ -35702,7 +35530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C28" s="5" t="s">
         <v>339</v>
       </c>
@@ -35722,7 +35550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C29" s="5" t="s">
         <v>338</v>
       </c>
@@ -35742,7 +35570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>201</v>
       </c>
@@ -35768,7 +35596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C31" s="5" t="s">
         <v>339</v>
       </c>
@@ -35788,7 +35616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C32" s="5" t="s">
         <v>338</v>
       </c>
@@ -35808,7 +35636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>199</v>
       </c>
@@ -35834,7 +35662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C34" s="5" t="s">
         <v>339</v>
       </c>
@@ -35854,7 +35682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C35" s="5" t="s">
         <v>338</v>
       </c>
@@ -35874,7 +35702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>198</v>
       </c>
@@ -35900,7 +35728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C37" s="5" t="s">
         <v>339</v>
       </c>
@@ -35920,7 +35748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C38" s="5" t="s">
         <v>338</v>
       </c>
@@ -35940,7 +35768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>197</v>
       </c>
@@ -35966,7 +35794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C40" s="5" t="s">
         <v>339</v>
       </c>
@@ -35986,7 +35814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C41" s="5" t="s">
         <v>338</v>
       </c>
@@ -36006,7 +35834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>203</v>
       </c>
@@ -36032,7 +35860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C43" s="5" t="s">
         <v>339</v>
       </c>
@@ -36052,7 +35880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C44" s="5" t="s">
         <v>338</v>
       </c>
@@ -36072,7 +35900,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
         <v>102</v>
       </c>
@@ -36095,7 +35923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C46" s="5" t="s">
         <v>339</v>
       </c>
@@ -36115,7 +35943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C47" s="5" t="s">
         <v>338</v>
       </c>
@@ -36135,7 +35963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>192</v>
       </c>
@@ -36161,7 +35989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C49" s="5" t="s">
         <v>339</v>
       </c>
@@ -36181,7 +36009,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>202</v>
       </c>
@@ -36207,7 +36035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C51" s="5" t="s">
         <v>339</v>
       </c>
@@ -36227,7 +36055,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>182</v>
       </c>
@@ -36253,12 +36081,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C53" s="5" t="s">
         <v>339</v>
       </c>
       <c r="D53" s="90">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="E53" s="90">
         <v>0</v>
@@ -36306,7 +36134,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>196</v>
       </c>
@@ -36337,7 +36165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C58" s="5" t="s">
         <v>339</v>
       </c>
@@ -36359,7 +36187,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C59" s="5" t="s">
         <v>338</v>
       </c>
@@ -36381,7 +36209,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>193</v>
       </c>
@@ -36407,7 +36235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C61" s="5" t="s">
         <v>338</v>
       </c>
@@ -36427,7 +36255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B62" s="5" t="s">
         <v>6</v>
       </c>
@@ -36450,7 +36278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C63" s="5" t="s">
         <v>338</v>
       </c>
@@ -36470,7 +36298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>184</v>
       </c>
@@ -36496,7 +36324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C65" s="5" t="s">
         <v>338</v>
       </c>
@@ -36516,7 +36344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B66" s="5" t="s">
         <v>6</v>
       </c>
@@ -36539,7 +36367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C67" s="5" t="s">
         <v>338</v>
       </c>
@@ -36559,7 +36387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>204</v>
       </c>
@@ -36585,7 +36413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C69" s="5" t="s">
         <v>338</v>
       </c>
@@ -36608,7 +36436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B70" s="5" t="s">
         <v>6</v>
       </c>
@@ -36636,7 +36464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C71" s="5" t="s">
         <v>338</v>
       </c>
@@ -36659,7 +36487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>167</v>
       </c>
@@ -36690,7 +36518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C73" s="5" t="s">
         <v>338</v>
       </c>
@@ -37514,7 +37342,7 @@
         <v>339</v>
       </c>
       <c r="D108" s="90">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E108" s="90">
         <v>0</v>
@@ -38775,7 +38603,7 @@
         <v>339</v>
       </c>
       <c r="D163" s="90">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="E163" s="90">
         <v>0</v>
@@ -38791,7 +38619,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="DUNt8zA99i1ftvMu7nhPdvRqKB3aTg6fJoNdJrO4wLU4tiiIhe0ISZxXsInDP/1JgH7oo69TyNVLsCJyQtLIGA==" saltValue="Jv7DYcoprjujOnGMPx4mMA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0geJcWX+Iu4P2ZF+SHnA3k5viOvACRnZIG+q4ECcjWl+gZdTyUi43E2NqL/nVI5dvUGbXIDwyj2xbYwN1SWU3w==" saltValue="jL37xWzPX6ZzSMiolfK6Jg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -38836,7 +38664,7 @@
       </c>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>166</v>
       </c>
@@ -38860,7 +38688,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C3" s="8" t="s">
         <v>339</v>
       </c>
@@ -38878,7 +38706,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>189</v>
       </c>
@@ -38902,7 +38730,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C5" s="8" t="s">
         <v>339</v>
       </c>
@@ -38920,7 +38748,7 @@
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>188</v>
       </c>
@@ -38944,7 +38772,7 @@
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C7" s="8" t="s">
         <v>339</v>
       </c>
@@ -38988,7 +38816,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>166</v>
       </c>
@@ -39015,7 +38843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C12" s="8" t="s">
         <v>339</v>
       </c>
@@ -39032,7 +38860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>189</v>
       </c>
@@ -39059,7 +38887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C14" s="8" t="s">
         <v>339</v>
       </c>
@@ -39080,7 +38908,7 @@
         <v>0.53100000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>188</v>
       </c>
@@ -39107,7 +38935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C16" s="8" t="s">
         <v>339</v>
       </c>
@@ -39154,7 +38982,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>166</v>
       </c>
@@ -39181,7 +39009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C21" s="8" t="s">
         <v>339</v>
       </c>
@@ -39198,7 +39026,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>189</v>
       </c>
@@ -39225,7 +39053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C23" s="8" t="s">
         <v>339</v>
       </c>
@@ -39246,7 +39074,7 @@
         <v>0.64900000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>188</v>
       </c>
@@ -39273,7 +39101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C25" s="8" t="s">
         <v>339</v>
       </c>
@@ -39295,7 +39123,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/G+XRu5T2NaciAWvUcZgFukEiLCNbkwvWz4ndneclFSfewlwZBmmbG5ce9Q4rmW5V9dFnPf3nMRxzHTlQNxgKw==" saltValue="tldju3vAQ0jGW1Yn1YT+/g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="IQQdIkGJ4OD+TztQ9cmyatoUz8z2QUI8ucQ/dIUBnvfHo42utsQD0giGn91vCuBPPEqTGCpNE2ObpWmJB7SSyg==" saltValue="0dP63aQPtOpalz4O3oUwYQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -39317,7 +39145,7 @@
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="str">
         <f>"Porcentaje de muertes en el año de referencia ("&amp;start_year&amp;") atribuible a la causa"</f>
-        <v>Porcentaje de muertes en el año de referencia (2021) atribuible a la causa</v>
+        <v>Porcentaje de muertes en el año de referencia (2024) atribuible a la causa</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -39345,7 +39173,7 @@
         <v>93</v>
       </c>
       <c r="C3" s="55">
-        <v>7.7852531721108861E-3</v>
+        <v>2.822998082324844E-2</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39353,7 +39181,7 @@
         <v>97</v>
       </c>
       <c r="C4" s="101">
-        <v>0.1104314088841564</v>
+        <v>7.0228368574160885E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39361,7 +39189,7 @@
         <v>95</v>
       </c>
       <c r="C5" s="101">
-        <v>8.2541916573618035E-2</v>
+        <v>0.1233726047836731</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39369,7 +39197,7 @@
         <v>91</v>
       </c>
       <c r="C6" s="101">
-        <v>0.329225287383837</v>
+        <v>0.26438892254695279</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39377,7 +39205,7 @@
         <v>96</v>
       </c>
       <c r="C7" s="101">
-        <v>0.26604515066131029</v>
+        <v>0.33964450408319652</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39385,7 +39213,7 @@
         <v>98</v>
       </c>
       <c r="C8" s="101">
-        <v>5.7428130468389543E-2</v>
+        <v>1.295647428162284E-2</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39393,7 +39221,7 @@
         <v>92</v>
       </c>
       <c r="C9" s="101">
-        <v>7.7054891446840759E-2</v>
+        <v>4.1254149538606392E-2</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39401,7 +39229,7 @@
         <v>94</v>
       </c>
       <c r="C10" s="101">
-        <v>6.9487961409737009E-2</v>
+        <v>0.1199249953685389</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39450,16 +39278,16 @@
         <v>84</v>
       </c>
       <c r="C14" s="55">
-        <v>0.14223879086630209</v>
+        <v>0.1596124108183756</v>
       </c>
       <c r="D14" s="55">
-        <v>0.14223879086630209</v>
+        <v>0.1596124108183756</v>
       </c>
       <c r="E14" s="55">
-        <v>0.14223879086630209</v>
+        <v>0.1596124108183756</v>
       </c>
       <c r="F14" s="55">
-        <v>0.14223879086630209</v>
+        <v>0.1596124108183756</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39467,16 +39295,16 @@
         <v>102</v>
       </c>
       <c r="C15" s="101">
-        <v>0.28748066796321281</v>
+        <v>0.2498034844866944</v>
       </c>
       <c r="D15" s="101">
-        <v>0.28748066796321281</v>
+        <v>0.2498034844866944</v>
       </c>
       <c r="E15" s="101">
-        <v>0.28748066796321281</v>
+        <v>0.2498034844866944</v>
       </c>
       <c r="F15" s="101">
-        <v>0.28748066796321281</v>
+        <v>0.2498034844866944</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39484,16 +39312,16 @@
         <v>2</v>
       </c>
       <c r="C16" s="101">
-        <v>5.0147283635475083E-2</v>
+        <v>4.6704185577370237E-2</v>
       </c>
       <c r="D16" s="101">
-        <v>5.0147283635475083E-2</v>
+        <v>4.6704185577370237E-2</v>
       </c>
       <c r="E16" s="101">
-        <v>5.0147283635475083E-2</v>
+        <v>4.6704185577370237E-2</v>
       </c>
       <c r="F16" s="101">
-        <v>5.0147283635475083E-2</v>
+        <v>4.6704185577370237E-2</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39501,16 +39329,16 @@
         <v>90</v>
       </c>
       <c r="C17" s="101">
-        <v>1.485571103059875E-2</v>
+        <v>7.825061005128861E-2</v>
       </c>
       <c r="D17" s="101">
-        <v>1.485571103059875E-2</v>
+        <v>7.825061005128861E-2</v>
       </c>
       <c r="E17" s="101">
-        <v>1.485571103059875E-2</v>
+        <v>7.825061005128861E-2</v>
       </c>
       <c r="F17" s="101">
-        <v>1.485571103059875E-2</v>
+        <v>7.825061005128861E-2</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39518,16 +39346,16 @@
         <v>3</v>
       </c>
       <c r="C18" s="101">
-        <v>0.113311026172252</v>
+        <v>0.22146118708923121</v>
       </c>
       <c r="D18" s="101">
-        <v>0.113311026172252</v>
+        <v>0.22146118708923121</v>
       </c>
       <c r="E18" s="101">
-        <v>0.113311026172252</v>
+        <v>0.22146118708923121</v>
       </c>
       <c r="F18" s="101">
-        <v>0.113311026172252</v>
+        <v>0.22146118708923121</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39535,16 +39363,16 @@
         <v>101</v>
       </c>
       <c r="C19" s="101">
-        <v>2.0832431100539759E-2</v>
+        <v>2.327848719104594E-2</v>
       </c>
       <c r="D19" s="101">
-        <v>2.0832431100539759E-2</v>
+        <v>2.327848719104594E-2</v>
       </c>
       <c r="E19" s="101">
-        <v>2.0832431100539759E-2</v>
+        <v>2.327848719104594E-2</v>
       </c>
       <c r="F19" s="101">
-        <v>2.0832431100539759E-2</v>
+        <v>2.327848719104594E-2</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39552,16 +39380,16 @@
         <v>79</v>
       </c>
       <c r="C20" s="101">
-        <v>5.6682828741777803E-2</v>
+        <v>6.2088160097453382E-2</v>
       </c>
       <c r="D20" s="101">
-        <v>5.6682828741777803E-2</v>
+        <v>6.2088160097453382E-2</v>
       </c>
       <c r="E20" s="101">
-        <v>5.6682828741777803E-2</v>
+        <v>6.2088160097453382E-2</v>
       </c>
       <c r="F20" s="101">
-        <v>5.6682828741777803E-2</v>
+        <v>6.2088160097453382E-2</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39569,16 +39397,16 @@
         <v>88</v>
       </c>
       <c r="C21" s="101">
-        <v>8.5374155968913248E-2</v>
+        <v>3.8913994294759342E-2</v>
       </c>
       <c r="D21" s="101">
-        <v>8.5374155968913248E-2</v>
+        <v>3.8913994294759342E-2</v>
       </c>
       <c r="E21" s="101">
-        <v>8.5374155968913248E-2</v>
+        <v>3.8913994294759342E-2</v>
       </c>
       <c r="F21" s="101">
-        <v>8.5374155968913248E-2</v>
+        <v>3.8913994294759342E-2</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39586,16 +39414,16 @@
         <v>99</v>
       </c>
       <c r="C22" s="101">
-        <v>0.22907710452092839</v>
+        <v>0.1198874803937814</v>
       </c>
       <c r="D22" s="101">
-        <v>0.22907710452092839</v>
+        <v>0.1198874803937814</v>
       </c>
       <c r="E22" s="101">
-        <v>0.22907710452092839</v>
+        <v>0.1198874803937814</v>
       </c>
       <c r="F22" s="101">
-        <v>0.22907710452092839</v>
+        <v>0.1198874803937814</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39604,19 +39432,19 @@
       </c>
       <c r="C23" s="48">
         <f>SUM(C14:C22)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D23" s="48">
         <f>SUM(D14:D22)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="E23" s="48">
         <f>SUM(E14:E22)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="F23" s="48">
         <f>SUM(F14:F22)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
@@ -39728,7 +39556,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="aJPRJil0NisOI6gZWmr4Zy3mgjo6WXGDKgdyEV+wpUonYTPlzintLGSL2zF0Cmf8XhDDhsSc4pEw509dju4Rbw==" saltValue="XHT33TcIkG93BaA8ZF/bXw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wxWt30JAY+iX9hnTHirtCx0a+YKlmaubuaLAoz3aLiD+6AWqaW32B9Ih4ukLqLILqR02Uvi9IlRCJtI3N9GxTg==" saltValue="Sk6CQ8lgvV0RfdP7Gy1Bgg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -39750,7 +39578,7 @@
     <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="str">
         <f>"Porcentaje de población en cada categoría en el año de referencia ("&amp;start_year&amp;")"</f>
-        <v>Porcentaje de población en cada categoría en el año de referencia (2021)</v>
+        <v>Porcentaje de población en cada categoría en el año de referencia (2024)</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>120</v>
@@ -39780,23 +39608,23 @@
       </c>
       <c r="C2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C4:C5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.57247399084166029</v>
+        <v>0.57247405346602631</v>
       </c>
       <c r="D2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D4:D5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.57247399084166029</v>
+        <v>0.57247405346602631</v>
       </c>
       <c r="E2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E4:E5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.47509587476377879</v>
+        <v>0.47423758481127021</v>
       </c>
       <c r="F2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F4:F5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.30851661402352026</v>
+        <v>0.30851657807595168</v>
       </c>
       <c r="G2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G4:G5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.27250172408455453</v>
+        <v>0.27250176789555769</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39805,23 +39633,23 @@
       </c>
       <c r="C3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C4:C5), 0, 1) + 1, 0, 1, TRUE) - SUM(C4:C5), "")</f>
-        <v>0.30905727751657031</v>
+        <v>0.30905724653397371</v>
       </c>
       <c r="D3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D4:D5), 0, 1) + 1, 0, 1, TRUE) - SUM(D4:D5), "")</f>
-        <v>0.30905727751657031</v>
+        <v>0.30905724653397371</v>
       </c>
       <c r="E3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E4:E5), 0, 1) + 1, 0, 1, TRUE) - SUM(E4:E5), "")</f>
-        <v>0.35066215773696513</v>
+        <v>0.35096571518872982</v>
       </c>
       <c r="F3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F4:F5), 0, 1) + 1, 0, 1, TRUE) - SUM(F4:F5), "")</f>
-        <v>0.38292492192618677</v>
+        <v>0.38292492192404837</v>
       </c>
       <c r="G3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G4:G5), 0, 1) + 1, 0, 1, TRUE) - SUM(G4:G5), "")</f>
-        <v>0.3809793272412435</v>
+        <v>0.38097933210444235</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39829,19 +39657,19 @@
         <v>110</v>
       </c>
       <c r="C4" s="45">
-        <v>4.7722220420837402E-2</v>
+        <v>4.7722199999999999E-2</v>
       </c>
       <c r="D4" s="53">
-        <v>4.7722220420837402E-2</v>
+        <v>4.7722199999999999E-2</v>
       </c>
       <c r="E4" s="53">
-        <v>8.7833374738693196E-2</v>
+        <v>8.8112999999999997E-2</v>
       </c>
       <c r="F4" s="53">
-        <v>0.153509572148323</v>
+        <v>0.1535096</v>
       </c>
       <c r="G4" s="53">
-        <v>0.150337129831314</v>
+        <v>0.1503371</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39849,19 +39677,19 @@
         <v>106</v>
       </c>
       <c r="C5" s="45">
-        <v>7.0746511220931993E-2</v>
+        <v>7.0746500000000004E-2</v>
       </c>
       <c r="D5" s="53">
-        <v>7.0746511220931993E-2</v>
+        <v>7.0746500000000004E-2</v>
       </c>
       <c r="E5" s="53">
-        <v>8.6408592760562897E-2</v>
+        <v>8.6683699999999989E-2</v>
       </c>
       <c r="F5" s="53">
-        <v>0.15504889190196999</v>
+        <v>0.15504889999999999</v>
       </c>
       <c r="G5" s="53">
-        <v>0.19618181884288799</v>
+        <v>0.19618179999999999</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39889,23 +39717,23 @@
       </c>
       <c r="C8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C10:C11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.43845576271655351</v>
+        <v>0.44153491459137839</v>
       </c>
       <c r="D8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D10:D11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.43845576271655351</v>
+        <v>0.44153491459137839</v>
       </c>
       <c r="E8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E10:E11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.34813286014513767</v>
+        <v>0.34987316643445965</v>
       </c>
       <c r="F8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F10:F11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.40303041241498305</v>
+        <v>0.39824863492985318</v>
       </c>
       <c r="G8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G10:G11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.41271241511184598</v>
+        <v>0.4067842096375015</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39914,23 +39742,23 @@
       </c>
       <c r="C9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C10:C11), 0, 1) + 1, 0, 1, TRUE) - SUM(C10:C11), "")</f>
-        <v>0.36252075955031093</v>
+        <v>0.36161358540862165</v>
       </c>
       <c r="D9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D10:D11), 0, 1) + 1, 0, 1, TRUE) - SUM(D10:D11), "")</f>
-        <v>0.36252075955031093</v>
+        <v>0.36161358540862165</v>
       </c>
       <c r="E9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E10:E11), 0, 1) + 1, 0, 1, TRUE) - SUM(E10:E11), "")</f>
-        <v>0.38081490598006429</v>
+        <v>0.38063053356554033</v>
       </c>
       <c r="F9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F10:F11), 0, 1) + 1, 0, 1, TRUE) - SUM(F10:F11), "")</f>
-        <v>0.37169177629618316</v>
+        <v>0.37274316507014682</v>
       </c>
       <c r="G9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G10:G11), 0, 1) + 1, 0, 1, TRUE) - SUM(G10:G11), "")</f>
-        <v>0.3694234365693867</v>
+        <v>0.37083429036249849</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39938,19 +39766,19 @@
         <v>107</v>
       </c>
       <c r="C10" s="45">
-        <v>0.112000979483128</v>
+        <v>0.11077869999999999</v>
       </c>
       <c r="D10" s="53">
-        <v>0.112000979483128</v>
+        <v>0.11077869999999999</v>
       </c>
       <c r="E10" s="53">
-        <v>0.15598480403423301</v>
+        <v>0.15586839999999999</v>
       </c>
       <c r="F10" s="53">
-        <v>0.12805274128913899</v>
+        <v>0.12830440000000001</v>
       </c>
       <c r="G10" s="53">
-        <v>0.123658940196037</v>
+        <v>0.12531539999999999</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39958,19 +39786,19 @@
         <v>119</v>
       </c>
       <c r="C11" s="45">
-        <v>8.7022498250007588E-2</v>
+        <v>8.6072799999999991E-2</v>
       </c>
       <c r="D11" s="53">
-        <v>8.7022498250007588E-2</v>
+        <v>8.6072799999999991E-2</v>
       </c>
       <c r="E11" s="53">
-        <v>0.11506742984056501</v>
+        <v>0.1136279</v>
       </c>
       <c r="F11" s="53">
-        <v>9.722506999969481E-2</v>
+        <v>0.1007038</v>
       </c>
       <c r="G11" s="53">
-        <v>9.4205208122730311E-2</v>
+        <v>9.7066099999999989E-2</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -40147,7 +39975,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="rt2pQaF+sdVJMbxjAIHctqpxiKXqf0ZN2/TkXp4XXDrltXu0S2CbjtLAMUPitB1olKT/OWfmCumjsh3pbSomeQ==" saltValue="7ZO+0l/Quhp5k55wu3acvw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wTYiHro/bb29JajHXiW7tKD2d0XPerqGEnfj+tnY44oVfEMHUSh+jcx5eZsNKuVv6c0DMaAtwOLaAbM+U3iEeg==" saltValue="jMlW3njeCzbmRoHsyMhEug==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40169,7 +39997,7 @@
     <row r="1" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="str">
         <f>"Porcentaje de niños en cada categoría en el año de referencia ("&amp;start_year&amp;")"</f>
-        <v>Porcentaje de niños en cada categoría en el año de referencia (2021)</v>
+        <v>Porcentaje de niños en cada categoría en el año de referencia (2024)</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>120</v>
@@ -40198,64 +40026,78 @@
         <v>124</v>
       </c>
       <c r="C2" s="45">
-        <v>0.61253422498703003</v>
+        <v>0.61253420000000003</v>
       </c>
       <c r="D2" s="53">
         <v>0.41144239999999999</v>
       </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
+      <c r="E2" s="53">
+        <v>0</v>
+      </c>
+      <c r="F2" s="53">
+        <v>0</v>
+      </c>
+      <c r="G2" s="53">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>127</v>
       </c>
       <c r="C3" s="53">
-        <v>0.22120472788810699</v>
+        <v>0.2212047</v>
       </c>
       <c r="D3" s="53">
         <v>0.29817589999999999</v>
       </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
+      <c r="E3" s="53">
+        <v>0</v>
+      </c>
+      <c r="F3" s="53">
+        <v>0</v>
+      </c>
+      <c r="G3" s="53">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C4" s="53">
-        <v>7.4739158153533894E-2</v>
+        <v>7.4739199999999992E-2</v>
       </c>
       <c r="D4" s="53">
         <v>0.23041149999999999</v>
       </c>
       <c r="E4" s="53">
-        <v>0.90059196949005094</v>
+        <v>0.90059200000000006</v>
       </c>
       <c r="F4" s="53">
-        <v>0.61897557973861705</v>
-      </c>
-      <c r="G4" s="53"/>
+        <v>0.61897559999999996</v>
+      </c>
+      <c r="G4" s="53">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>125</v>
       </c>
       <c r="C5" s="52">
-        <v>9.1521896421909291E-2</v>
+        <v>9.1521899999999989E-2</v>
       </c>
       <c r="D5" s="52">
-        <v>5.9970259666442899E-2</v>
+        <v>5.9970299999999997E-2</v>
       </c>
       <c r="E5" s="52">
         <f>1-SUM(E2:E4)</f>
-        <v>9.9408030509949064E-2</v>
+        <v>9.9407999999999941E-2</v>
       </c>
       <c r="F5" s="52">
         <f>1-SUM(F2:F4)</f>
-        <v>0.38102442026138295</v>
+        <v>0.38102440000000004</v>
       </c>
       <c r="G5" s="52">
         <f>1-SUM(G2:G4)</f>
@@ -40263,7 +40105,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Gjd46MGHHRFvNAoFdoc6CRN4Vd5XddmXL9qCGGwoNKbKGPhOKTcqrPhkxiaZHGymw++szQIgiES4kmM3scAEsQ==" saltValue="KaAx/XAvxQMSsqGf7tD6UQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="16m96Q+ragEn6y71RFyA0yy8VtWz9I0QXodvlLnQ04SfTph2qvpYDZHXvaYGG6PYTZeXffKwZPytUvBN4y5xJw==" saltValue="LpVyy+645uvbYz2sb3vCBw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -40316,7 +40158,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -40333,10 +40175,10 @@
       <c r="J2" s="23"/>
       <c r="K2" s="23"/>
     </row>
-    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>138</v>
       </c>
@@ -40353,10 +40195,10 @@
       <c r="J4" s="23"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>128</v>
       </c>
@@ -40373,7 +40215,7 @@
       <c r="J6" s="23"/>
       <c r="K6" s="23"/>
     </row>
-    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>104</v>
       </c>
@@ -40387,7 +40229,7 @@
       <c r="J7" s="23"/>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>139</v>
       </c>
@@ -40401,7 +40243,7 @@
       <c r="J8" s="23"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>134</v>
       </c>
@@ -40418,7 +40260,7 @@
       <c r="J10" s="23"/>
       <c r="K10" s="23"/>
     </row>
-    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>131</v>
       </c>
@@ -40432,7 +40274,7 @@
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
     </row>
-    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>37</v>
       </c>
@@ -40449,7 +40291,7 @@
       <c r="J13" s="23"/>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
         <v>132</v>
       </c>
@@ -40464,7 +40306,7 @@
       <c r="K14" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JLNDRPwVZveMIciw+OZFGXiVyMBOJN5Jb79/IXCKw/gm6Vca2RfVXpArQTLbO8Vz0i7ckfkACYtNnAshdzN6Dw==" saltValue="oenDsL3Y7TCseRHQNcjckA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="u1tDw7xAgdNcSsL77RY9NM8zpbif4+qv4DwOAsxhRqwxDFpE2d53nkczL+sYUYMUwaaOwwz/nzWFD7lLeD+7bg==" saltValue="Z9dCcVffVOyBwxtyIAXW3g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait"/>
 </worksheet>
@@ -40490,7 +40332,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>144</v>
       </c>
@@ -40498,7 +40340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>143</v>
       </c>
@@ -40506,7 +40348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>142</v>
       </c>
@@ -40514,7 +40356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>146</v>
       </c>
@@ -40522,7 +40364,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>140</v>
       </c>
@@ -40530,7 +40372,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>141</v>
       </c>
@@ -40539,7 +40381,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="qHYpsed5pp6PXJJRyZ7bKaiw2xRTbpH2hGGdeFT6fMOpPzLh2iV6tJtmGnlwr09DGMVE7EfHphdhii8KvlMg4Q==" saltValue="OY7sDDd9hOZb8TGF2Qf7ZQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+Ml2BKMgFq8FGSFCEKRL+QFbQ02/0CMWeM9ZC4k6DjohFs+Yz9v+07pe2PAxsfaLGEyloThHexbZjKhRYfjydg==" saltValue="E384yVsSQ+yILC/BL6h/cg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -40591,7 +40433,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" s="32" t="s">
         <v>78</v>
       </c>
@@ -40604,7 +40446,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="32" t="s">
         <v>74</v>
       </c>
@@ -40617,29 +40459,33 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
         <v>77</v>
       </c>
       <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
+      <c r="D5" s="47" t="s">
+        <v>5</v>
+      </c>
       <c r="E5" s="38" t="str">
         <f>IF(E$7="","",E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="32" t="s">
         <v>75</v>
       </c>
       <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
+      <c r="D6" s="47" t="s">
+        <v>5</v>
+      </c>
       <c r="E6" s="38" t="str">
         <f>IF(E$7="","",E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" s="32" t="s">
         <v>148</v>
       </c>
@@ -40661,7 +40507,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="32" t="s">
         <v>78</v>
       </c>
@@ -40672,7 +40518,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" s="32" t="s">
         <v>74</v>
       </c>
@@ -40683,7 +40529,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="32" t="s">
         <v>77</v>
       </c>
@@ -40696,7 +40542,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" s="32" t="s">
         <v>75</v>
       </c>
@@ -40709,7 +40555,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14" s="32" t="s">
         <v>148</v>
       </c>
@@ -40733,7 +40579,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="32" t="s">
         <v>78</v>
       </c>
@@ -40746,7 +40592,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="32" t="s">
         <v>74</v>
       </c>
@@ -40759,7 +40605,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="32" t="s">
         <v>77</v>
       </c>
@@ -40772,7 +40618,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="32" t="s">
         <v>75</v>
       </c>
@@ -40785,7 +40631,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="32" t="s">
         <v>148</v>
       </c>
@@ -40794,7 +40640,7 @@
       <c r="E21" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="lyA+KEkreNgrIgYVEvkLU6cycZXb0XUaxe/5Q0BmRmgRCG3TD3pffmb6hCnIQjkkl1kMfJojZUmOgJWmG26wVA==" saltValue="OEEiJtGoBG9GCM35EG7ZsQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ktUSLo7hO4ujsqBatHpjoaIz4LONnPTNRGF1ALV1sJOBc7sVG+RxMC1avvWBlTdlsUsS0Eq/+gBZqPiLSQCEgg==" saltValue="GXOI+MK3OiYOpBGlRetNpA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -40853,7 +40699,7 @@
       <c r="D3" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cbGSXPctqGDUfYNKz0g0Aegj7BN04LnBSEYVxnLjzhTVHOsrtAPxlITXJNDK0IWQmFnQkubd5Puxv1hkIuNEVA==" saltValue="QyGBGNR9xqFU3NdZYKV1kQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="RXB53e7eZ144LrMmUTdBV47aKSmlbRvga2CW2SaDiyPx2ruHUp9665wDGG88dHAvlfPQbmhWWjaYs25q2q7gww==" saltValue="XOYv/2eKWKH+QPOCpLn98A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inputs/es/LiST countries/SSD_databook.xlsx
+++ b/inputs/es/LiST countries/SSD_databook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\es\LiST countries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{359E1B06-C90E-46E3-A240-DDE1D4B0C30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B62AE52-141A-4CA2-87FF-8B6554AB616D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10180" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entradas de población-año base" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Distribución estado nutricional" sheetId="4" r:id="rId4"/>
     <sheet name="Distribución de lactancia" sheetId="5" r:id="rId5"/>
     <sheet name="Tendencias temporales" sheetId="6" r:id="rId6"/>
-    <sheet name="Variables económicas   " sheetId="7" r:id="rId7"/>
+    <sheet name="Variables económicas" sheetId="7" r:id="rId7"/>
     <sheet name="Paquetes de IYCF" sheetId="8" r:id="rId8"/>
     <sheet name="Tratamiento de la MAS" sheetId="9" r:id="rId9"/>
     <sheet name="Costo y cobertura del programa" sheetId="10" r:id="rId10"/>
@@ -20814,6 +20814,35 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="AvP8TwSAUbTUyAG2RaSvmbYEhP/hw3KY5u5h3xsvGHyUsERUnQf/NCwXmX12eM7P+HsgDKvz1SA1cmYYKksEmA==" saltValue="R/De7/V+AURb9384i29rqw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="B142:B144"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B117:B119"/>
     <mergeCell ref="B111:B113"/>
@@ -20830,35 +20859,6 @@
     <mergeCell ref="B98:B100"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B89:B91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -41619,16 +41619,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f77cb9dc30d15950233dec29875e7d3d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c7972fb108f377c3e0c6a81e726e76be" ns2:_="">
     <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
@@ -41812,6 +41802,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -41822,16 +41822,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1364B1-D0AC-4AFC-8837-019122E84913}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89AE9A51-FA73-431C-A4D5-36C1DFA1FEFD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41849,6 +41839,16 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1364B1-D0AC-4AFC-8837-019122E84913}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA00B2B-FC7F-4ED6-BC3D-3DE83488E245}">
   <ds:schemaRefs>

--- a/inputs/es/LiST countries/SSD_databook.xlsx
+++ b/inputs/es/LiST countries/SSD_databook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\es\LiST countries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modelling projects\Nutrition\inputs\es\LiST countries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F67E23F4-F31F-49B2-AC8E-EA43B6AE7CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD724C66-D237-4FCB-9F6D-A87E3CBAF010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entradas de población-año base" sheetId="1" r:id="rId1"/>
@@ -2690,6 +2690,74 @@
         </r>
       </text>
     </comment>
+    <comment ref="L37" authorId="1" shapeId="0" xr:uid="{B53E2CCE-449F-4B13-937B-3F8B887F6752}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M37" authorId="1" shapeId="0" xr:uid="{1148A5A1-251A-4064-B40F-0C8735779040}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N37" authorId="1" shapeId="0" xr:uid="{15C867EE-F338-4C14-9C7D-F0E3CF1EF5FB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O37" authorId="1" shapeId="0" xr:uid="{8E4E4ECE-5F5C-4FD8-8945-6257CBFF139B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
       <text>
         <r>
@@ -3928,7 +3996,7 @@
     <author>Nick Scott</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{6BB5D3EA-EB2C-4557-A77A-BC3B31DE5A74}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{E6EBA730-3C9A-42F5-8372-C12E3D2BCF23}">
       <text>
         <r>
           <rPr>
@@ -3942,7 +4010,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{8276B184-5391-46AC-9017-CD45ED68E7E2}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{AF9DB01E-B712-4A66-A517-1C057B372D40}">
       <text>
         <r>
           <rPr>
@@ -3956,7 +4024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{70662288-9B2B-4D49-A059-B389A408D887}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{207C9149-2C56-40E5-890F-83153B938A2F}">
       <text>
         <r>
           <rPr>
@@ -3970,7 +4038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{5F99FF59-4E44-4847-82EE-D42B7418AA00}">
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{39C4CB92-7EE0-4046-B67E-41191387FFA0}">
       <text>
         <r>
           <rPr>
@@ -3984,7 +4052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{F6C9465E-FBDE-45D1-8394-CD6F9C9C2529}">
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{E377B1E7-A333-4A74-97C3-029328512C07}">
       <text>
         <r>
           <rPr>
@@ -3998,7 +4066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{8724D448-9507-4D14-BCA7-F21B3CAF1BD6}">
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{200C4BAB-9EE2-447E-A6DD-80717CFE4AC8}">
       <text>
         <r>
           <rPr>
@@ -4012,7 +4080,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{1D086CE7-3639-4C5A-8FD3-DB935503731C}">
+    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{9FC7E5D2-2D8B-4961-9B75-5691D4A68B0C}">
       <text>
         <r>
           <rPr>
@@ -4026,7 +4094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G6" authorId="1" shapeId="0" xr:uid="{1EDBAC82-3035-4B47-8DB4-6C9605D373FF}">
+    <comment ref="G6" authorId="1" shapeId="0" xr:uid="{D951D76C-28E5-48CE-899C-D128152950FC}">
       <text>
         <r>
           <rPr>
@@ -4040,7 +4108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{F889FFDD-F5D3-428F-97C9-3FA317F4DEEC}">
+    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{E9DCEC9B-12F6-42CF-8CD9-B1C5DD42DE71}">
       <text>
         <r>
           <rPr>
@@ -4054,7 +4122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G8" authorId="1" shapeId="0" xr:uid="{178C61B9-10CF-475E-AE2A-1148BD159501}">
+    <comment ref="G8" authorId="1" shapeId="0" xr:uid="{9FD33C3F-D78F-4E9D-A67C-9D39AC73491A}">
       <text>
         <r>
           <rPr>
@@ -4068,7 +4136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{D1ADD6AA-00B3-496F-889D-6AD9E8EC7261}">
+    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{3400288E-DF03-41FF-B1F2-3EB20AA1B927}">
       <text>
         <r>
           <rPr>
@@ -4082,7 +4150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="1" shapeId="0" xr:uid="{D8A7821F-2C8B-4B9F-B2CF-783B6F1D6ACB}">
+    <comment ref="G10" authorId="1" shapeId="0" xr:uid="{9C325214-076C-49F4-9A1C-FDD39C7EF1F6}">
       <text>
         <r>
           <rPr>
@@ -4096,7 +4164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{30A88894-D578-48EA-8642-A1FBFF69A3C1}">
+    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{9B6733C4-FA93-4154-8674-5B85D19B6115}">
       <text>
         <r>
           <rPr>
@@ -4110,7 +4178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="1" shapeId="0" xr:uid="{1FC0B5F8-9FC2-4095-AEC3-321F62EB13E4}">
+    <comment ref="G12" authorId="1" shapeId="0" xr:uid="{0607EB3C-B9C7-4D01-AE82-3B20B34591B6}">
       <text>
         <r>
           <rPr>
@@ -4124,7 +4192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{037243D6-BCDE-4F6B-AFCC-3F94A0DD5E02}">
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{26DD0551-BD1F-450A-8953-951E786BA725}">
       <text>
         <r>
           <rPr>
@@ -4138,7 +4206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{DE335ADC-5DD3-496C-A5AC-AAE47036457E}">
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{07B0F43C-E3A4-41A5-9220-14111D4DE5D5}">
       <text>
         <r>
           <rPr>
@@ -4152,7 +4220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{2912EBE3-D556-42B6-96D5-24EC21E6156C}">
+    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{BF774CA2-E4B3-46E6-A04D-901C8156EE77}">
       <text>
         <r>
           <rPr>
@@ -4166,7 +4234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{4CB9182B-79CD-4596-8295-56AF4E3846AB}">
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{DDFF231A-B050-4E30-B877-4FB8473D71B0}">
       <text>
         <r>
           <rPr>
@@ -4180,7 +4248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{80F6289A-949B-4FAE-AC85-22980BCEA4F4}">
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{0214BC76-CC8A-414C-8D7A-C51B3E742D6B}">
       <text>
         <r>
           <rPr>
@@ -4204,7 +4272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{96FCBC9B-E5EC-46B8-8DF3-3E8D35EE350D}">
+    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{408E5496-8B3D-4F1E-BD84-9A9255C25832}">
       <text>
         <r>
           <rPr>
@@ -4218,7 +4286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="1" shapeId="0" xr:uid="{93171B53-CE10-41E2-9E96-E27147D4D778}">
+    <comment ref="F22" authorId="1" shapeId="0" xr:uid="{DF0EEE5A-AAEC-4832-9B3D-B069B0FD3D24}">
       <text>
         <r>
           <rPr>
@@ -4232,7 +4300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{5FE03E37-E69F-43F4-B94E-7BBC3063A87D}">
+    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{2A9C86D6-9952-4010-8EF5-ED482E1554FE}">
       <text>
         <r>
           <rPr>
@@ -4247,7 +4315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{626B60BA-B78A-4BE5-ACC0-D15C014DDDE7}">
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{5A70274A-2FB2-4238-A065-120459AD1B15}">
       <text>
         <r>
           <rPr>
@@ -4262,7 +4330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{A6D7FDB2-70C1-4A3F-AE05-E1F583DAC911}">
+    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{385F9BE4-A3AC-4198-BAC3-722E7A520402}">
       <text>
         <r>
           <rPr>
@@ -4277,7 +4345,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D30" authorId="1" shapeId="0" xr:uid="{73FE6ADA-DBBD-4E18-9E0A-7E9F1B65F4FF}">
+    <comment ref="D30" authorId="1" shapeId="0" xr:uid="{1E0B57C8-7A0A-48E3-A3E8-1E19A7175498}">
       <text>
         <r>
           <rPr>
@@ -4292,7 +4360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{36DC02C6-7D52-483D-9E4D-A62E1832D1E9}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{2AC9637A-4534-4154-9BD7-3AE7DD8CD9DD}">
       <text>
         <r>
           <rPr>
@@ -4307,7 +4375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{3A418ECB-CB98-4DAE-914F-181BDF7ED565}">
+    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{01A3CEF9-0D30-4FDB-AF26-2DC31C7D29F6}">
       <text>
         <r>
           <rPr>
@@ -4322,7 +4390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G30" authorId="1" shapeId="0" xr:uid="{F54E6507-D7CB-4F8D-8BA0-8C678AC88484}">
+    <comment ref="G30" authorId="1" shapeId="0" xr:uid="{E3448607-813B-4893-BFAF-1777B6724FBF}">
       <text>
         <r>
           <rPr>
@@ -4337,7 +4405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H30" authorId="1" shapeId="0" xr:uid="{51D136EC-624C-44D3-B5B3-53EE7A4C79F4}">
+    <comment ref="H30" authorId="1" shapeId="0" xr:uid="{CB33591A-EF28-41CE-A9F1-ECF332B1A04F}">
       <text>
         <r>
           <rPr>
@@ -4352,7 +4420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{0358037B-23C7-469B-B136-BD3C312D371A}">
+    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{652EDCEE-9F4F-4011-BE3F-87A81AEAB68F}">
       <text>
         <r>
           <rPr>
@@ -4366,7 +4434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{83DD7CE2-EBA6-4C72-A5A2-1E7961104F35}">
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{F2E7DF39-BD3C-4774-9BD5-66837E9E22BF}">
       <text>
         <r>
           <rPr>
@@ -4380,7 +4448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{D00C0728-6CE5-4232-9E9D-03298AA7E83F}">
+    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{84346A43-22E1-4209-86B7-5484553C9A3C}">
       <text>
         <r>
           <rPr>
@@ -4394,7 +4462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G45" authorId="0" shapeId="0" xr:uid="{DE005C0A-2F8A-418C-851E-64B2B8CFE1FA}">
+    <comment ref="G45" authorId="0" shapeId="0" xr:uid="{6AA73D8B-E906-4C63-9A89-433F265EDADB}">
       <text>
         <r>
           <rPr>
@@ -4408,7 +4476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H45" authorId="0" shapeId="0" xr:uid="{E55324F7-370C-4385-ADBA-E8B0EBEB4BEC}">
+    <comment ref="H45" authorId="0" shapeId="0" xr:uid="{D0DB495D-46B4-4957-B9C2-D1B5214046C5}">
       <text>
         <r>
           <rPr>
@@ -4422,7 +4490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D46" authorId="0" shapeId="0" xr:uid="{F53439F8-F18B-45A1-B265-14A4B9BFCA4E}">
+    <comment ref="D46" authorId="0" shapeId="0" xr:uid="{E8F934AE-F36A-4978-A2B4-5231B12CD33F}">
       <text>
         <r>
           <rPr>
@@ -4436,7 +4504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{D3552897-BBD5-4175-B68A-A3F1E4A6E75C}">
+    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{53D9CECE-9FA0-4330-B76A-C6EEC6C1D659}">
       <text>
         <r>
           <rPr>
@@ -4450,7 +4518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{CC47941B-D047-44AD-8609-225A3A1207CF}">
+    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{9DC905D6-8DE5-4FE7-BE6F-D3E934A75201}">
       <text>
         <r>
           <rPr>
@@ -4464,7 +4532,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G46" authorId="0" shapeId="0" xr:uid="{0CBE3706-3924-4509-A583-88069D4C218C}">
+    <comment ref="G46" authorId="0" shapeId="0" xr:uid="{ACC4B3F7-E558-402F-BE57-0C3DDC8060F5}">
       <text>
         <r>
           <rPr>
@@ -4478,7 +4546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H46" authorId="0" shapeId="0" xr:uid="{A5F6F3D3-D70F-4D04-A795-6D6BF5E34983}">
+    <comment ref="H46" authorId="0" shapeId="0" xr:uid="{955FA18E-86F7-422C-8CA5-A38FE4881347}">
       <text>
         <r>
           <rPr>
@@ -4492,7 +4560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{DD598447-A738-4E83-BE84-12132D14A7E3}">
+    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{33441C3A-E101-49E5-A4DB-504F222DBABB}">
       <text>
         <r>
           <rPr>
@@ -4507,7 +4575,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{AAC1265A-FBA5-4B61-B6FD-C1ADAB02C015}">
+    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{9A6BDF27-568B-45B9-BE8D-362C80D286A5}">
       <text>
         <r>
           <rPr>
@@ -4522,7 +4590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{CB5BEA38-52BE-4279-8999-876D134092DA}">
+    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{08FA6FC1-5E34-45F1-9F8B-4E7BAEF15D4E}">
       <text>
         <r>
           <rPr>
@@ -4537,7 +4605,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{EEC82E46-7238-472F-8156-89C286EC0CC5}">
+    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{E9730E75-4547-4DE1-A9F2-FCA6D5B09778}">
       <text>
         <r>
           <rPr>
@@ -4552,7 +4620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{9AD99541-38BF-452C-BBDF-30A63672B134}">
+    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{38945CFE-2923-4A7C-9E0E-820E103F12F0}">
       <text>
         <r>
           <rPr>
@@ -4567,7 +4635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{9F2485E2-4FB1-40DF-95BC-EF307614F383}">
+    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{F76610CF-AE5A-4A2B-BD5A-C60057991BBE}">
       <text>
         <r>
           <rPr>
@@ -4583,7 +4651,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{5A344499-6486-4E45-BC00-E472735A7CB2}">
+    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{8EC67AD9-5004-458A-B78A-27343190877D}">
       <text>
         <r>
           <rPr>
@@ -4599,7 +4667,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{031BB5AD-8138-4687-BD78-7EBC20A98663}">
+    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{8D6C5816-8BDB-4D07-A205-24F2394A4590}">
       <text>
         <r>
           <rPr>
@@ -4615,7 +4683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{184A5B5A-1F15-44FE-898C-B90309E01D89}">
+    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{B76A1BFB-64B6-4C17-9732-138D8EB49340}">
       <text>
         <r>
           <rPr>
@@ -4631,7 +4699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{8ED585B4-389F-460E-8916-C9CBE4D87E3D}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{962C7931-87AA-452E-BF56-06BF5EBED30C}">
       <text>
         <r>
           <rPr>
@@ -4647,7 +4715,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{AD24A257-1231-432A-9AC2-49A1BBCFE8E5}">
+    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{25F108DC-6C32-4B96-9492-1B12A3709CE9}">
       <text>
         <r>
           <rPr>
@@ -4662,7 +4730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{A07ED250-D084-453F-8461-66EC0C10E110}">
+    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{8B1376CD-B39F-49F6-BC5B-7A2858E0592C}">
       <text>
         <r>
           <rPr>
@@ -4677,7 +4745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{9059BCA8-1FD3-4E64-86A7-3061E1F307E3}">
+    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{048CF327-553B-4B14-8A84-22CC73D47D4A}">
       <text>
         <r>
           <rPr>
@@ -4692,7 +4760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G53" authorId="0" shapeId="0" xr:uid="{7052734F-4036-424E-8991-EAD18C6FC7CF}">
+    <comment ref="G53" authorId="0" shapeId="0" xr:uid="{1FFD936D-DA45-475C-9F30-391304B2787A}">
       <text>
         <r>
           <rPr>
@@ -4707,7 +4775,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{9211745A-0C8C-4E89-B62F-2D6F1D5B7D01}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{3CED59C7-FFD8-4D8E-9210-1FB3B9F57245}">
       <text>
         <r>
           <rPr>
@@ -4722,7 +4790,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D55" authorId="1" shapeId="0" xr:uid="{5423B35A-FBAB-43E1-A574-44F7790EAEA1}">
+    <comment ref="D55" authorId="1" shapeId="0" xr:uid="{BFC97A30-BB96-4307-90EA-5BE03611C63A}">
       <text>
         <r>
           <rPr>
@@ -4736,7 +4804,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{9923839E-0345-401E-8DBE-0D84F514E4A9}">
+    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{51ED88B2-1E5E-47FC-9698-0E5AB645D504}">
       <text>
         <r>
           <rPr>
@@ -4750,7 +4818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G60" authorId="0" shapeId="0" xr:uid="{BA7FE3E3-08B4-4F16-B01F-05A523005C56}">
+    <comment ref="G60" authorId="0" shapeId="0" xr:uid="{561CB528-6BAE-4817-8CC0-243735B76FA1}">
       <text>
         <r>
           <rPr>
@@ -4764,7 +4832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H60" authorId="0" shapeId="0" xr:uid="{6D26BBC2-8403-47E0-89A8-CCA5B5E2A63F}">
+    <comment ref="H60" authorId="0" shapeId="0" xr:uid="{E496632C-74C0-41C8-9AB4-0B4C87893674}">
       <text>
         <r>
           <rPr>
@@ -4778,7 +4846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{4063B8B9-975B-4060-938A-48F03FAEF419}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{FBF69FC4-CD17-4513-AF48-E695A29BF824}">
       <text>
         <r>
           <rPr>
@@ -4792,7 +4860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G61" authorId="0" shapeId="0" xr:uid="{50660BAB-9FCC-42B5-9F93-0DBB8CA89897}">
+    <comment ref="G61" authorId="0" shapeId="0" xr:uid="{900E651E-9020-4856-BB60-BF507FACE1CC}">
       <text>
         <r>
           <rPr>
@@ -4806,7 +4874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H61" authorId="0" shapeId="0" xr:uid="{C6A07F78-8D75-479F-926E-474BA841B234}">
+    <comment ref="H61" authorId="0" shapeId="0" xr:uid="{49F9B2F7-6FD6-4FDF-921C-425B5CDD5155}">
       <text>
         <r>
           <rPr>
@@ -4820,7 +4888,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{FA86AF70-4991-447A-BCAA-1000A44BF256}">
+    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{4AC52846-7242-459E-9C8D-BF78F201C110}">
       <text>
         <r>
           <rPr>
@@ -4834,7 +4902,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{FD47D524-CA3E-4654-B95C-882313C71EE4}">
+    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{B7E52F08-0E63-474C-A17D-FB71B12C1A4F}">
       <text>
         <r>
           <rPr>
@@ -4848,7 +4916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{350D10EC-94B3-4790-8891-B0A27313C3E5}">
+    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{329CDC5B-FBD8-45AA-9D30-2F9915F0B0DB}">
       <text>
         <r>
           <rPr>
@@ -4862,7 +4930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{E54F70F0-DBA3-4F25-90EB-D1DFD3641E6A}">
+    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{74D24310-E8B6-4724-B08F-C246A0B86F17}">
       <text>
         <r>
           <rPr>
@@ -4876,7 +4944,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{77363AFB-2A43-477F-8EB8-CC2F7E3ECEA0}">
+    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{7026E01B-E53C-4032-904B-4C8C6143328A}">
       <text>
         <r>
           <rPr>
@@ -4890,7 +4958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{01109C22-04ED-4FDB-949C-C34810AB2E95}">
+    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{56E6B52D-1C74-48A6-AB95-D033A5B5881A}">
       <text>
         <r>
           <rPr>
@@ -4904,7 +4972,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F69" authorId="1" shapeId="0" xr:uid="{72F3E256-254B-4FFC-9E01-1752BCF475A6}">
+    <comment ref="F69" authorId="1" shapeId="0" xr:uid="{A2996F6D-43C2-499B-8B4D-F7E668692366}">
       <text>
         <r>
           <rPr>
@@ -4918,7 +4986,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G69" authorId="1" shapeId="0" xr:uid="{E057EF81-59F3-42CB-9D3F-907D93019067}">
+    <comment ref="G69" authorId="1" shapeId="0" xr:uid="{1BA30CAA-FFAB-42ED-B857-7C2DBF6DD53A}">
       <text>
         <r>
           <rPr>
@@ -4932,7 +5000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{DF457454-4973-4207-9E3D-7D50D7830FDE}">
+    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{234E5DD0-50F5-435F-A2AD-FDCE2659B300}">
       <text>
         <r>
           <rPr>
@@ -4946,7 +5014,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{0A31E4B1-743B-4208-AE2B-4146BBD81A93}">
+    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{81B268C8-266C-41E0-8968-7FD59EF44415}">
       <text>
         <r>
           <rPr>
@@ -4960,7 +5028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{BA5122FC-4C8D-49F0-9902-8C88B2457CA4}">
+    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{D68CDFE1-6866-4AC0-B4D7-B34E1A995637}">
       <text>
         <r>
           <rPr>
@@ -4974,7 +5042,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{EB775666-1A82-4D30-A432-4C033A1A7AED}">
+    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{6447B983-C337-44DD-BE06-3BF10916980C}">
       <text>
         <r>
           <rPr>
@@ -4988,7 +5056,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F77" authorId="1" shapeId="0" xr:uid="{98BB8C6D-B30B-4DB6-8B35-7D8DCE93E79C}">
+    <comment ref="F77" authorId="1" shapeId="0" xr:uid="{42AC3582-1D7E-471B-A6C7-CD7E77F8588B}">
       <text>
         <r>
           <rPr>
@@ -5003,7 +5071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F79" authorId="1" shapeId="0" xr:uid="{75544419-0995-4A7F-98E3-CBE19D6471D0}">
+    <comment ref="F79" authorId="1" shapeId="0" xr:uid="{C499C901-0DF0-4641-8493-EE778DE73B96}">
       <text>
         <r>
           <rPr>
@@ -5018,7 +5086,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{866B3636-D1B7-40EE-A9B3-22FD1891C340}">
+    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{080FF01F-34D3-44B7-835E-C7CC7A5B457C}">
       <text>
         <r>
           <rPr>
@@ -5033,7 +5101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D83" authorId="0" shapeId="0" xr:uid="{3C5743BD-EFCC-4AF2-B330-6FDF8775A9D5}">
+    <comment ref="D83" authorId="0" shapeId="0" xr:uid="{B263C3DB-9806-4F53-B7FE-F5AB30086A04}">
       <text>
         <r>
           <rPr>
@@ -5048,7 +5116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D85" authorId="0" shapeId="0" xr:uid="{07C4191C-0E34-4B64-AAF8-A7F551741AB2}">
+    <comment ref="D85" authorId="0" shapeId="0" xr:uid="{FF88E7CE-1D54-4693-9AC1-0680C2879226}">
       <text>
         <r>
           <rPr>
@@ -5063,7 +5131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D87" authorId="1" shapeId="0" xr:uid="{419B2D75-98C1-46B5-842D-118FC911FF04}">
+    <comment ref="D87" authorId="1" shapeId="0" xr:uid="{F32BE7CD-2AAA-47AD-914F-4CAAC1FEDD3B}">
       <text>
         <r>
           <rPr>
@@ -5078,7 +5146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E87" authorId="1" shapeId="0" xr:uid="{A1CD6A7F-EF69-49BD-84EA-F060EB24114F}">
+    <comment ref="E87" authorId="1" shapeId="0" xr:uid="{BCFCAE2C-B071-4EBD-916E-9CB34A3AE95A}">
       <text>
         <r>
           <rPr>
@@ -5093,7 +5161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F87" authorId="1" shapeId="0" xr:uid="{D5825461-688C-438C-8542-BD85D579FDC7}">
+    <comment ref="F87" authorId="1" shapeId="0" xr:uid="{E2890E16-5EE9-49DE-B974-B3ADDC0025FE}">
       <text>
         <r>
           <rPr>
@@ -5108,7 +5176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G87" authorId="1" shapeId="0" xr:uid="{AF7C92B2-AC28-43C3-9C19-D68E37FF28FD}">
+    <comment ref="G87" authorId="1" shapeId="0" xr:uid="{FFC68E24-6D1B-4208-B66E-D8A12166F7EF}">
       <text>
         <r>
           <rPr>
@@ -5123,7 +5191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H87" authorId="1" shapeId="0" xr:uid="{700142E9-6A7D-415A-8AA2-F2A8B6A75555}">
+    <comment ref="H87" authorId="1" shapeId="0" xr:uid="{AE98D75E-0886-4415-A5FC-355EDA6C4FF5}">
       <text>
         <r>
           <rPr>
@@ -5138,7 +5206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D103" authorId="0" shapeId="0" xr:uid="{7D67AB3C-983B-47D0-9AFF-DA097636CBA4}">
+    <comment ref="D103" authorId="0" shapeId="0" xr:uid="{F3FF4EFF-507E-406A-9019-C50AD187D27F}">
       <text>
         <r>
           <rPr>
@@ -5152,7 +5220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E103" authorId="0" shapeId="0" xr:uid="{38FC6B21-5384-4027-AE29-F2FF12011A26}">
+    <comment ref="E103" authorId="0" shapeId="0" xr:uid="{DE5B9A2C-A2CF-41B4-A227-60CE716BCCA3}">
       <text>
         <r>
           <rPr>
@@ -5166,7 +5234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F103" authorId="0" shapeId="0" xr:uid="{EB3D123B-E86C-4173-B872-21E041277078}">
+    <comment ref="F103" authorId="0" shapeId="0" xr:uid="{34EEDC69-740F-43FD-A983-6FB9711FB123}">
       <text>
         <r>
           <rPr>
@@ -5180,7 +5248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G103" authorId="0" shapeId="0" xr:uid="{C5BAFDF7-3C0B-454A-B8DD-17A5272728F7}">
+    <comment ref="G103" authorId="0" shapeId="0" xr:uid="{C1C7CF2A-6820-4496-B5B3-46A027800BF9}">
       <text>
         <r>
           <rPr>
@@ -5194,7 +5262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H103" authorId="0" shapeId="0" xr:uid="{BB84B4E6-6EBF-43F8-A27F-ABACD68A728A}">
+    <comment ref="H103" authorId="0" shapeId="0" xr:uid="{EBC10A23-30BF-4E42-8CA2-8EE10D6CA31A}">
       <text>
         <r>
           <rPr>
@@ -5208,7 +5276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{BFD18A89-7D4A-4FA5-8D9C-46BDFC49F7B4}">
+    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{C4570B06-D8B9-4BF0-8899-481D28F107D4}">
       <text>
         <r>
           <rPr>
@@ -5223,7 +5291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{1ABF9016-F3C2-48B1-BD46-AD89F4003AC8}">
+    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{E10AAA50-CCAF-4DFB-8CEA-438EA6695142}">
       <text>
         <r>
           <rPr>
@@ -5238,7 +5306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{6A6E8E29-2989-40FF-B168-55803883F0D8}">
+    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{0D2DBAA3-0B85-4069-9696-DDECC83557DF}">
       <text>
         <r>
           <rPr>
@@ -5253,7 +5321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{48DA76B4-3665-4A45-819A-BFEEFF70E5D8}">
+    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{E6F4F3F2-6816-43AD-9558-8D77B03CE641}">
       <text>
         <r>
           <rPr>
@@ -5268,7 +5336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{B80ED8C6-87BC-498B-8629-005BCCE79F4B}">
+    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{994813E0-DC6E-4867-8FA2-13765D152F5E}">
       <text>
         <r>
           <rPr>
@@ -5283,7 +5351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D108" authorId="0" shapeId="0" xr:uid="{B5F2ED77-4534-4005-9653-3943813A8B21}">
+    <comment ref="D108" authorId="0" shapeId="0" xr:uid="{6D709644-E2DA-4998-B8D6-CCE8241FA062}">
       <text>
         <r>
           <rPr>
@@ -5299,7 +5367,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E108" authorId="0" shapeId="0" xr:uid="{76285A74-606B-4904-9089-8C072E19A125}">
+    <comment ref="E108" authorId="0" shapeId="0" xr:uid="{E0BF8484-6C50-4B90-B5C7-81D81EF18053}">
       <text>
         <r>
           <rPr>
@@ -5315,7 +5383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F108" authorId="0" shapeId="0" xr:uid="{63134AD8-900C-4178-BB9D-773F5A2AEB3B}">
+    <comment ref="F108" authorId="0" shapeId="0" xr:uid="{98B23DB2-DC71-4976-B9E0-A2E971751C45}">
       <text>
         <r>
           <rPr>
@@ -5331,7 +5399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G108" authorId="0" shapeId="0" xr:uid="{E4550204-DAD5-4F24-9613-4B653BB1BEF9}">
+    <comment ref="G108" authorId="0" shapeId="0" xr:uid="{EED7AE56-914C-4919-99D9-9B4DD94D01A5}">
       <text>
         <r>
           <rPr>
@@ -5347,7 +5415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H108" authorId="0" shapeId="0" xr:uid="{8EB04C99-52A7-4C56-9738-8833ED4CF79E}">
+    <comment ref="H108" authorId="0" shapeId="0" xr:uid="{C946989D-0B8C-452F-9FD8-02724BD02182}">
       <text>
         <r>
           <rPr>
@@ -5363,7 +5431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D110" authorId="0" shapeId="0" xr:uid="{1E087D6A-9C87-4366-B106-9662D0E9F522}">
+    <comment ref="D110" authorId="0" shapeId="0" xr:uid="{E509D43A-5096-49C2-BA18-0C199C6BF4A8}">
       <text>
         <r>
           <rPr>
@@ -5378,7 +5446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E110" authorId="0" shapeId="0" xr:uid="{9524A10F-3B35-4B50-9361-07DEAF9EC66F}">
+    <comment ref="E110" authorId="0" shapeId="0" xr:uid="{7D8578B9-425B-43DC-B215-7EF10F08E80C}">
       <text>
         <r>
           <rPr>
@@ -5393,7 +5461,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{00995C78-B5BF-45A5-8F02-B4D6CB8053C5}">
+    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{309E82E0-67AD-454E-9A05-4D9313B66A93}">
       <text>
         <r>
           <rPr>
@@ -5408,7 +5476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G110" authorId="0" shapeId="0" xr:uid="{B614B807-4445-457C-8B76-0D078F087764}">
+    <comment ref="G110" authorId="0" shapeId="0" xr:uid="{B9EF8017-E5A0-4B1E-9AF7-1E695ECA49AB}">
       <text>
         <r>
           <rPr>
@@ -5423,7 +5491,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H110" authorId="0" shapeId="0" xr:uid="{4A9ECB14-4CB2-41BF-A402-F7A28029EC10}">
+    <comment ref="H110" authorId="0" shapeId="0" xr:uid="{26E77479-1563-4266-B2C1-17AF174C9575}">
       <text>
         <r>
           <rPr>
@@ -5438,7 +5506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D112" authorId="1" shapeId="0" xr:uid="{B642BE55-802D-4C94-B750-1AEA253BACA7}">
+    <comment ref="D112" authorId="1" shapeId="0" xr:uid="{09D666FE-E28F-48AE-ADF8-2D96C595DB94}">
       <text>
         <r>
           <rPr>
@@ -5452,7 +5520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{CE9B9D72-3B1C-4412-9D79-6D0874D60CEE}">
+    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{B9267817-21CE-42E6-A675-E3EF4A926E99}">
       <text>
         <r>
           <rPr>
@@ -5466,7 +5534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G117" authorId="0" shapeId="0" xr:uid="{AB5427B8-7880-46F7-8737-0E11C545B3E1}">
+    <comment ref="G117" authorId="0" shapeId="0" xr:uid="{D5F41D35-9589-4734-9273-1246C82D90D3}">
       <text>
         <r>
           <rPr>
@@ -5480,7 +5548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H117" authorId="0" shapeId="0" xr:uid="{7DADC3D7-B312-4F80-917D-FD030194B70F}">
+    <comment ref="H117" authorId="0" shapeId="0" xr:uid="{68C36586-6425-44D5-AE71-7B83AC0B0D80}">
       <text>
         <r>
           <rPr>
@@ -5494,7 +5562,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{E932DAA3-B84B-48A0-A350-BB68775D7800}">
+    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{EAF8C373-AE13-4606-898A-ED625C16452F}">
       <text>
         <r>
           <rPr>
@@ -5508,7 +5576,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{75AFBBA3-C0BF-47C9-96C1-E2BCE0A5518C}">
+    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{A99AB4B1-F894-4133-B7CD-69537AC87FC8}">
       <text>
         <r>
           <rPr>
@@ -5522,7 +5590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H118" authorId="0" shapeId="0" xr:uid="{44B4DAC8-1128-45E5-B99C-C84974BBEE0A}">
+    <comment ref="H118" authorId="0" shapeId="0" xr:uid="{66812343-2E7C-44E8-B27C-8CF88CE05138}">
       <text>
         <r>
           <rPr>
@@ -5536,7 +5604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{BFC250B8-BAEB-445C-954D-7BE97AABDFDB}">
+    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{384DF3D1-4AA8-4943-A530-5AAE715E42E7}">
       <text>
         <r>
           <rPr>
@@ -5550,7 +5618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{AEC7DAF2-9B1C-4CBB-B735-E9AB7A0CFD03}">
+    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{1DE26347-7149-43FD-858E-465A040CC0F3}">
       <text>
         <r>
           <rPr>
@@ -5564,7 +5632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{5757C298-3224-4FCB-AE44-57AE2804657A}">
+    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{B687D13E-D130-42E7-9D6A-3F80F0C7EF5D}">
       <text>
         <r>
           <rPr>
@@ -5578,7 +5646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{32018E11-B6CC-4CB9-AD83-CDEAB15CB02F}">
+    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{9BC31D67-F810-46D7-B5A1-4288AAC1F5B6}">
       <text>
         <r>
           <rPr>
@@ -5592,7 +5660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F124" authorId="1" shapeId="0" xr:uid="{548CA939-8049-4A22-8DCF-97B43275D455}">
+    <comment ref="F124" authorId="1" shapeId="0" xr:uid="{64D245B3-8DA5-40BE-BC14-2456737D9F8E}">
       <text>
         <r>
           <rPr>
@@ -5606,7 +5674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G124" authorId="1" shapeId="0" xr:uid="{B79D2BBE-1689-4CA2-9F3C-27F21A096995}">
+    <comment ref="G124" authorId="1" shapeId="0" xr:uid="{5798986F-DE4D-469D-8D38-C4A254954155}">
       <text>
         <r>
           <rPr>
@@ -5620,7 +5688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F126" authorId="1" shapeId="0" xr:uid="{521B8842-9FA3-4AE6-9999-7E38BD5734E2}">
+    <comment ref="F126" authorId="1" shapeId="0" xr:uid="{1683DE01-9F25-40E0-AE29-344104540630}">
       <text>
         <r>
           <rPr>
@@ -5634,7 +5702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G126" authorId="1" shapeId="0" xr:uid="{745C521C-CEC3-4590-B658-F244E03502B3}">
+    <comment ref="G126" authorId="1" shapeId="0" xr:uid="{6E399964-9FF6-4F4D-B47E-AC805C54B9BA}">
       <text>
         <r>
           <rPr>
@@ -5648,7 +5716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F128" authorId="0" shapeId="0" xr:uid="{48501DF5-33AD-4137-BF61-A1ACEF3712BB}">
+    <comment ref="F128" authorId="0" shapeId="0" xr:uid="{EFF89D0F-5E10-4447-B0BA-64F660AD6D14}">
       <text>
         <r>
           <rPr>
@@ -5662,7 +5730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G128" authorId="0" shapeId="0" xr:uid="{52DA180B-0E50-41F0-B433-76D057FD32AA}">
+    <comment ref="G128" authorId="0" shapeId="0" xr:uid="{E024415B-2F81-4A00-9886-75203AC76837}">
       <text>
         <r>
           <rPr>
@@ -5676,7 +5744,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F130" authorId="0" shapeId="0" xr:uid="{1827DF80-3E7F-4FAE-B545-321A48A20B7F}">
+    <comment ref="F130" authorId="0" shapeId="0" xr:uid="{773BC8B9-C7FD-4E1D-BFAD-28167A2B0241}">
       <text>
         <r>
           <rPr>
@@ -5690,7 +5758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G130" authorId="0" shapeId="0" xr:uid="{428ADF28-94CB-45A6-B512-653753D79D4A}">
+    <comment ref="G130" authorId="0" shapeId="0" xr:uid="{E0893EE6-8215-43BF-B8DC-C2BA125EF501}">
       <text>
         <r>
           <rPr>
@@ -5704,7 +5772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F134" authorId="1" shapeId="0" xr:uid="{E327363C-87BF-426D-8031-8E5B15B868F6}">
+    <comment ref="F134" authorId="1" shapeId="0" xr:uid="{B0106407-B25E-404E-AE98-C6E846DE7439}">
       <text>
         <r>
           <rPr>
@@ -5719,7 +5787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F136" authorId="1" shapeId="0" xr:uid="{0FC0F10D-E16C-4929-8C9C-BBCE7D585B2C}">
+    <comment ref="F136" authorId="1" shapeId="0" xr:uid="{B3781CC1-6735-4678-95E3-B6650A0CF979}">
       <text>
         <r>
           <rPr>
@@ -5734,7 +5802,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D138" authorId="0" shapeId="0" xr:uid="{83AA2241-D1A0-473B-BB01-4502DE008F6C}">
+    <comment ref="D138" authorId="0" shapeId="0" xr:uid="{550CF970-1632-472E-99A6-5157A6C70FB5}">
       <text>
         <r>
           <rPr>
@@ -5749,7 +5817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D140" authorId="0" shapeId="0" xr:uid="{AB840D19-E9DC-41E5-8B1A-28772D27BB6F}">
+    <comment ref="D140" authorId="0" shapeId="0" xr:uid="{0F529DF4-B0D9-4A77-880D-52378457049B}">
       <text>
         <r>
           <rPr>
@@ -5764,7 +5832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D142" authorId="0" shapeId="0" xr:uid="{28DA7237-5B4A-4888-B612-1517D8E4181A}">
+    <comment ref="D142" authorId="0" shapeId="0" xr:uid="{0A749486-D0DA-44DD-A158-4937B013D9E1}">
       <text>
         <r>
           <rPr>
@@ -5779,7 +5847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D144" authorId="1" shapeId="0" xr:uid="{24B15358-0318-4650-A1D9-ACBF45D6BD86}">
+    <comment ref="D144" authorId="1" shapeId="0" xr:uid="{65A87F96-9920-4AFF-9D42-432A9BC46A37}">
       <text>
         <r>
           <rPr>
@@ -5794,7 +5862,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E144" authorId="1" shapeId="0" xr:uid="{3CCBD856-2028-4562-873C-EF798B7CEB0E}">
+    <comment ref="E144" authorId="1" shapeId="0" xr:uid="{14AFEBEB-6E6D-485B-AD84-D77832449F6B}">
       <text>
         <r>
           <rPr>
@@ -5809,7 +5877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F144" authorId="1" shapeId="0" xr:uid="{515C103F-DDC3-40D5-AA24-3704C957FBDF}">
+    <comment ref="F144" authorId="1" shapeId="0" xr:uid="{C956521D-520C-46E0-BBF9-22BA4AB5823B}">
       <text>
         <r>
           <rPr>
@@ -5824,7 +5892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G144" authorId="1" shapeId="0" xr:uid="{2B07245A-D9DE-402F-8C94-59F9204780AD}">
+    <comment ref="G144" authorId="1" shapeId="0" xr:uid="{889435D0-F1CE-49D5-B3FA-2C346C3DD8BB}">
       <text>
         <r>
           <rPr>
@@ -5839,7 +5907,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H144" authorId="1" shapeId="0" xr:uid="{B09F6ACE-9930-4B23-AC49-D976E3AF6D20}">
+    <comment ref="H144" authorId="1" shapeId="0" xr:uid="{21DCB560-D7D0-454D-9256-2EB6BA5D9FAF}">
       <text>
         <r>
           <rPr>
@@ -5854,7 +5922,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D160" authorId="0" shapeId="0" xr:uid="{08D07A70-B0BF-4318-BF4F-F0DBC6170F84}">
+    <comment ref="D160" authorId="0" shapeId="0" xr:uid="{2CA48B3A-F458-496E-A12E-9EDFF9710F14}">
       <text>
         <r>
           <rPr>
@@ -5868,7 +5936,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E160" authorId="0" shapeId="0" xr:uid="{76EC0005-9898-4CC7-A802-EC15F25448F0}">
+    <comment ref="E160" authorId="0" shapeId="0" xr:uid="{D5130B5B-6564-4541-AFF7-B31DC2A99F0C}">
       <text>
         <r>
           <rPr>
@@ -5882,7 +5950,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F160" authorId="0" shapeId="0" xr:uid="{E5FFA232-5153-4095-946B-DFA45A9FBF8C}">
+    <comment ref="F160" authorId="0" shapeId="0" xr:uid="{A87CEC0D-D5EC-411A-9E0A-45792CF26B1E}">
       <text>
         <r>
           <rPr>
@@ -5896,7 +5964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G160" authorId="0" shapeId="0" xr:uid="{AFCCFA07-E0EB-45D3-B7C0-514815792647}">
+    <comment ref="G160" authorId="0" shapeId="0" xr:uid="{F07A7990-2D7C-41E0-8069-25EED27A8B7D}">
       <text>
         <r>
           <rPr>
@@ -5910,7 +5978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H160" authorId="0" shapeId="0" xr:uid="{C392BCAD-8C69-4A4C-87EF-377772EECC28}">
+    <comment ref="H160" authorId="0" shapeId="0" xr:uid="{B9A5DC53-F533-4CB3-94F1-5C0DF398AC61}">
       <text>
         <r>
           <rPr>
@@ -5924,7 +5992,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D163" authorId="0" shapeId="0" xr:uid="{E3317A10-0BE4-48FF-9352-A01B5BA3FEE5}">
+    <comment ref="D163" authorId="0" shapeId="0" xr:uid="{F61BC170-6314-4BE8-BD27-ACBE21EC6D83}">
       <text>
         <r>
           <rPr>
@@ -5939,7 +6007,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E163" authorId="0" shapeId="0" xr:uid="{67EC6033-7BEB-4400-84EE-0A8533A907FD}">
+    <comment ref="E163" authorId="0" shapeId="0" xr:uid="{F2F9EF38-F3FC-4F8C-BAEA-4602406D7D4B}">
       <text>
         <r>
           <rPr>
@@ -5954,7 +6022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F163" authorId="0" shapeId="0" xr:uid="{E94FC89C-5249-427A-BE28-D6BFC2F81758}">
+    <comment ref="F163" authorId="0" shapeId="0" xr:uid="{03156B19-EF6A-4B80-952F-EA4B39906AB2}">
       <text>
         <r>
           <rPr>
@@ -5969,7 +6037,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G163" authorId="0" shapeId="0" xr:uid="{AA56A34D-E716-48F4-B898-FA37D2EF7D4D}">
+    <comment ref="G163" authorId="0" shapeId="0" xr:uid="{6C70B7FC-07DB-4AA6-AD5D-BA8D185F69A2}">
       <text>
         <r>
           <rPr>
@@ -5984,7 +6052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H163" authorId="0" shapeId="0" xr:uid="{90492BA0-E368-47BA-98D1-DF7E39D86EF5}">
+    <comment ref="H163" authorId="0" shapeId="0" xr:uid="{ECCF229F-BC05-441A-A8EC-996A647C989C}">
       <text>
         <r>
           <rPr>
@@ -5999,7 +6067,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D165" authorId="0" shapeId="0" xr:uid="{9CD81021-C7F5-4F80-9E36-5A372FBC35BF}">
+    <comment ref="D165" authorId="0" shapeId="0" xr:uid="{853363A1-995D-434E-99B9-CBFFCC587E17}">
       <text>
         <r>
           <rPr>
@@ -6015,7 +6083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E165" authorId="0" shapeId="0" xr:uid="{49DF1121-32A1-4036-AEE8-BCAAA6147B06}">
+    <comment ref="E165" authorId="0" shapeId="0" xr:uid="{D7049EC9-BADF-40DE-979A-0A74E0293BB1}">
       <text>
         <r>
           <rPr>
@@ -6031,7 +6099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F165" authorId="0" shapeId="0" xr:uid="{9499DF21-B57E-420A-A749-CC9BF2D4D725}">
+    <comment ref="F165" authorId="0" shapeId="0" xr:uid="{C916B5A2-27DC-436D-B575-9210A24C214D}">
       <text>
         <r>
           <rPr>
@@ -6047,7 +6115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G165" authorId="0" shapeId="0" xr:uid="{4524A951-07DC-487B-A233-43D4EAAEC701}">
+    <comment ref="G165" authorId="0" shapeId="0" xr:uid="{D9F9FF7F-8008-4D79-ABB3-028FF22CD559}">
       <text>
         <r>
           <rPr>
@@ -6063,7 +6131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H165" authorId="0" shapeId="0" xr:uid="{889D9E25-29F0-4C18-931F-58D4600ECBE1}">
+    <comment ref="H165" authorId="0" shapeId="0" xr:uid="{D7D5CD6A-B8A4-4771-AAA0-5113E0A3BC1F}">
       <text>
         <r>
           <rPr>
@@ -6079,7 +6147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D167" authorId="0" shapeId="0" xr:uid="{678FE956-BF94-4DA4-81E3-20DDE72682D7}">
+    <comment ref="D167" authorId="0" shapeId="0" xr:uid="{06B708C5-CF4C-4BD9-A112-999F5C581700}">
       <text>
         <r>
           <rPr>
@@ -6094,7 +6162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E167" authorId="0" shapeId="0" xr:uid="{6CE9DBC0-F411-450C-ADE5-6FE43AB51348}">
+    <comment ref="E167" authorId="0" shapeId="0" xr:uid="{652C7700-A4E9-41DE-B7A6-091614D48006}">
       <text>
         <r>
           <rPr>
@@ -6109,7 +6177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F167" authorId="0" shapeId="0" xr:uid="{F2C8AB55-E76F-4187-99C2-69AB2BD9809A}">
+    <comment ref="F167" authorId="0" shapeId="0" xr:uid="{C648195E-E2CA-46F6-BED8-ABE76E4EB10D}">
       <text>
         <r>
           <rPr>
@@ -6124,7 +6192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G167" authorId="0" shapeId="0" xr:uid="{D025E63E-9D67-4225-8627-D53B10AA6DB9}">
+    <comment ref="G167" authorId="0" shapeId="0" xr:uid="{876F0647-9D39-464F-9AEF-66CCB9E7BEE5}">
       <text>
         <r>
           <rPr>
@@ -6139,7 +6207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H167" authorId="0" shapeId="0" xr:uid="{E220EC8B-3A48-4133-BD12-15E3EB9F00B6}">
+    <comment ref="H167" authorId="0" shapeId="0" xr:uid="{A2FD75B6-2FF3-4112-A257-87C89428A222}">
       <text>
         <r>
           <rPr>
@@ -6154,7 +6222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D169" authorId="1" shapeId="0" xr:uid="{74D29CD4-44A4-4706-B0D2-5EBDC4B70B6C}">
+    <comment ref="D169" authorId="1" shapeId="0" xr:uid="{17B0E3BD-602F-47AD-8FDA-505C553A7C4F}">
       <text>
         <r>
           <rPr>
@@ -9917,7 +9985,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="HUvf1+NqPVCn0/cQAMW5bPZiahyiNbc4Ox+SDt7yrpftl2BriiVlI9mRrJUWHrwp3//EUIGiwplPvJxYWGjfpw==" saltValue="KPmPFv9oH5uaUE69dP2zHw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wL7o60y6ZtaBwU6N/q1VuTCwbZT8dP1nZlirnjHTophLOCF9TW82kYp/DnmWa2zljeE7C3accnrQCu1d1RjBrA==" saltValue="Z78nTuZSmWGgl2eVKo4vEw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10842,7 +10910,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8W4ErrJnNRxP+b89S4+SIs0d9GAEnR8+hBgBsX9Z5LXMvEVoKhfuliqC4Pr3tgpCKNfdSisEpudKPrkfqre/cg==" saltValue="NRrqROMAvi9jurUvWsr2mQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vHQvjOWg5ZH3o21fKYaN/3uWZSICCM8MqeMJ8CuEwncSNwAHKF8MwlOcyuQHiQ8kblSv7ui4V3+jpj9axsQiNA==" saltValue="ddOlTccXYuRwpHpN4aoldA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10995,7 +11063,7 @@
       <c r="C20" s="58"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="o84qSVIafCcbkjl878Up8ZYi59eORELXqAt+6XYXa0d1p7WA6DG0sH6Llyqq0Lue02EftA2RLphtL1F2Rcm7Ng==" saltValue="LCK+SmEynKUZyVhrJ2nwxA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="d8j7iZxKKE6N6D2Jj1xy4N5A/kjT+v54cSem63f/UcbAmzn5tIIVui1XOwZHgXALusCUvDZ8M2gnKlCSRrBfJg==" saltValue="KcAM6b7jV7d/axUuEQ3VDQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -11093,7 +11161,7 @@
       <c r="A19" s="33"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="f5GtG7xpLUQepLXUv5s5sP7eFYGCjp87evKGjISeDMzKKIEVI4qG8LRJTHMttUO5lwNbM6FJ6eEtM7qsMMJMRQ==" saltValue="4plVjnlZSI6ab3y48H//Nw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bHbpfpKJQ8etDtfPyBFX1fa7WKwr4QFHCHRVWFWev7RIB3q3Kw7DUfBkVmV2uG70+FL0Nx1vYZJUltZCcH6Rzw==" saltValue="B5HUFUwgXV1AWfHvwSVxiA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -11203,7 +11271,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="o4vNewLWH6MPE6Joln0Rp2aXqz8M31wKD6ymerxB5iV3GatTzGSuD+Q+hViU3WeKa1KO7EWuynMukU2a/f6oqQ==" saltValue="+ayX+A4Vfs43d8JeoCa/kA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="UpkzPdSqErMKWYgIAyoTKjRpBzQ1ElSnD1x9j8nSFbh+kcoXW1+r9fM2cQhkKhPHA6NMExYzPWWmfxmLy0HNJA==" saltValue="dgoRk+ar5L5VHMjoKG025g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12961,7 +13029,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="N8TqLfTvqPEcCdDD5OU/7CiPiDwk43NebdkfmEG/piEcUbdu3AnDG0Fh6iDfAp/0G6MKOQA2B+C3lItJRixfWA==" saltValue="hWXJbmUjM93WQ8suhttGlA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Je0ErVxFqX8XaOHTHeLMK7Lsw84IGlwEArTkZdSjIBOOlnuF2GTBfas/jpLfb6Zugmt5K3wq4NE0/Wk0V0fVCA==" saltValue="ylt3mprTn6yeUvozCsTDFQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12994,7 +13062,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+anRw0UZjlfA0aVLGbge8Tsshunnxpab/EDNdhlkyMZ9pWTDxSGTcK0SzdX2PRdAoYbDglMsPkwdIa/aqS4zzw==" saltValue="xsSkR/VZsWsVSZOzxecI4A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ro/r+zndF/lTNvzCYZ860rzRtZfItR9SnjpzLiDO35HvPR3IHComwj62x4h1kiPwCNzt3VVLZpiX+3WMPvcT0A==" saltValue="dWgUZmpNRxuLphmCiqhe0A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13195,7 +13263,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="x4tSO0pPkpxUSg4nxWgaN+qV1lVFQnutybvQKobaGDZdA3bBvdS4lasken89hgkQhADmMqMmcYMDer4OCE6RYQ==" saltValue="B75sJiw5M4TFqJpkng5H5A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TnjTBwWWCU8D3RqtOTcfv1x9jf5Clh/0mHq0S6qzc9Yt3tesclsnCxxAFxR2UnO5TU0BC1VUWObrwev3VBuwqg==" saltValue="BKroT8z4PS8unLlOWd6e4Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -15005,7 +15073,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="FYVDpd3en/9cdwTh/ON8dVBDdrMJW5FQYdpi2x89iZGRP7IJ2VaNmiRF54YzqjdrErEX35mGlGZcbwS2z4Oajg==" saltValue="BBHrY8ZjfMU0Vi+3b2g+ow==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Z7oS7co35kBWIzpjMKnTe+WlKieKQd+1YOynygy0CCtkpyP3dR2hYP4X0Oh4Jt/yBL8kLXvo1TnbE6ZLiGORsQ==" saltValue="qDj9AZBsYaDirS76J0SNKw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15816,7 +15884,7 @@
       <c r="L39" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="0zfp5P0iHaVJcIIMs39ayKkHBl4mBg/ARGBKktyDKT7w/j/DL5aZbPKp2W35QgrvWH6pCschtmR/dfxW+bvpXg==" saltValue="Aa8xFoDX4cXgnwaSJQmtlQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fUSp3wzSlZH6AHwVhirJ+jRbVA7k27qm3WJzR4uxIrYQXs6WDv5RsgrS/xIrilhaNFy9xqjNcpUZS0qYaoRuzw==" saltValue="du70q61NJmWtst4NxoVKbA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16209,7 +16277,7 @@
       <c r="L14" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hLDqUosxEOR53vUF5H3a+CF2i/e2Zc9E4QqBHQEQEt4JYX0PaC31XKScV4LRTR5ZgYkbV1mBJv48vALE405EQQ==" saltValue="NnCg1WAsKF5SZvNmlmjhmA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="s55BU0kRRJq+azEkNzhAwDJm0zVWTzqTF92SljGw5vkq/a5Ho6P8xv3y3n/vRpeo/qoSPGyu4AcyoNvLZdO3Ug==" saltValue="DM3eZfJou2Zl8qHucuO+Ow==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16263,31 +16331,31 @@
         <v>2024</v>
       </c>
       <c r="B2" s="49">
-        <v>1573241.5</v>
+        <v>349013</v>
       </c>
       <c r="C2" s="49">
-        <v>407878</v>
+        <v>751321</v>
       </c>
       <c r="D2" s="49">
-        <v>687830.5</v>
+        <v>996666.5</v>
       </c>
       <c r="E2" s="49">
-        <v>1552358.5</v>
+        <v>607844</v>
       </c>
       <c r="F2" s="49">
-        <v>1028185.5</v>
+        <v>643870</v>
       </c>
       <c r="G2" s="17">
         <f t="shared" ref="G2:G13" si="0">C2+D2+E2+F2</f>
-        <v>3676252.5</v>
+        <v>2999701.5</v>
       </c>
       <c r="H2" s="17">
         <f t="shared" ref="H2:H13" si="1">(B2 + stillbirth*B2/(1000-stillbirth))/(1-abortion)</f>
-        <v>1835198.4369467765</v>
+        <v>407126.37702101382</v>
       </c>
       <c r="I2" s="17">
         <f t="shared" ref="I2:I13" si="2">G2-H2</f>
-        <v>1841054.0630532235</v>
+        <v>2592575.1229789862</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16296,31 +16364,31 @@
         <v>2025</v>
       </c>
       <c r="B3" s="49">
-        <v>349013</v>
+        <v>357711</v>
       </c>
       <c r="C3" s="50">
-        <v>751321</v>
+        <v>772056.5</v>
       </c>
       <c r="D3" s="50">
-        <v>996666.5</v>
+        <v>1067417.5</v>
       </c>
       <c r="E3" s="50">
-        <v>607844</v>
+        <v>609413</v>
       </c>
       <c r="F3" s="50">
-        <v>643870</v>
+        <v>647067.50000000012</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" si="0"/>
-        <v>2999701.5</v>
+        <v>3095954.5</v>
       </c>
       <c r="H3" s="17">
         <f t="shared" si="1"/>
-        <v>407126.37702101382</v>
+        <v>417272.66162166983</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" si="2"/>
-        <v>2592575.1229789862</v>
+        <v>2678681.8383783302</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16329,31 +16397,31 @@
         <v>2026</v>
       </c>
       <c r="B4" s="49">
-        <v>357711</v>
+        <v>365962</v>
       </c>
       <c r="C4" s="50">
-        <v>772056.5</v>
+        <v>791606.5</v>
       </c>
       <c r="D4" s="50">
-        <v>1067417.5</v>
+        <v>1138464.5</v>
       </c>
       <c r="E4" s="50">
-        <v>609413</v>
+        <v>618509</v>
       </c>
       <c r="F4" s="50">
-        <v>647067.50000000012</v>
+        <v>643815.49999999988</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="0"/>
-        <v>3095954.5</v>
+        <v>3192395.5</v>
       </c>
       <c r="H4" s="17">
         <f t="shared" si="1"/>
-        <v>417272.66162166983</v>
+        <v>426897.51724825223</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>2678681.8383783302</v>
+        <v>2765497.9827517476</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16362,31 +16430,31 @@
         <v>2027</v>
       </c>
       <c r="B5" s="49">
-        <v>365962</v>
+        <v>374205</v>
       </c>
       <c r="C5" s="50">
-        <v>791606.5</v>
+        <v>808787</v>
       </c>
       <c r="D5" s="50">
-        <v>1138464.5</v>
+        <v>1210033.5</v>
       </c>
       <c r="E5" s="50">
-        <v>618509</v>
+        <v>637482.5</v>
       </c>
       <c r="F5" s="50">
-        <v>643815.49999999988</v>
+        <v>632326</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="0"/>
-        <v>3192395.5</v>
+        <v>3288629</v>
       </c>
       <c r="H5" s="17">
         <f t="shared" si="1"/>
-        <v>426897.51724825223</v>
+        <v>436513.04081265879</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>2765497.9827517476</v>
+        <v>2852115.9591873414</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16395,31 +16463,31 @@
         <v>2028</v>
       </c>
       <c r="B6" s="49">
-        <v>374205</v>
+        <v>381724</v>
       </c>
       <c r="C6" s="50">
-        <v>808787</v>
+        <v>817985.5</v>
       </c>
       <c r="D6" s="50">
-        <v>1210033.5</v>
+        <v>1280200</v>
       </c>
       <c r="E6" s="50">
-        <v>637482.5</v>
+        <v>664496.5</v>
       </c>
       <c r="F6" s="50">
-        <v>632326</v>
+        <v>616443</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="0"/>
-        <v>3288629</v>
+        <v>3379125</v>
       </c>
       <c r="H6" s="17">
         <f t="shared" si="1"/>
-        <v>436513.04081265879</v>
+        <v>445284.0127501539</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>2852115.9591873414</v>
+        <v>2933840.9872498461</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16428,31 +16496,31 @@
         <v>2029</v>
       </c>
       <c r="B7" s="49">
-        <v>381724</v>
+        <v>389036</v>
       </c>
       <c r="C7" s="50">
-        <v>817985.5</v>
+        <v>816439.5</v>
       </c>
       <c r="D7" s="50">
-        <v>1280200</v>
+        <v>1343446.5</v>
       </c>
       <c r="E7" s="50">
-        <v>664496.5</v>
+        <v>695403</v>
       </c>
       <c r="F7" s="50">
-        <v>616443</v>
+        <v>605798</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="0"/>
-        <v>3379125</v>
+        <v>3461087</v>
       </c>
       <c r="H7" s="17">
         <f t="shared" si="1"/>
-        <v>445284.0127501539</v>
+        <v>453813.51757884986</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>2933840.9872498461</v>
+        <v>3007273.48242115</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16461,31 +16529,31 @@
         <v>2030</v>
       </c>
       <c r="B8" s="49">
-        <v>389036</v>
+        <v>395444</v>
       </c>
       <c r="C8" s="50">
-        <v>816439.5</v>
+        <v>802114.5</v>
       </c>
       <c r="D8" s="50">
-        <v>1343446.5</v>
+        <v>1398011.5</v>
       </c>
       <c r="E8" s="50">
-        <v>695403</v>
+        <v>732143.5</v>
       </c>
       <c r="F8" s="50">
-        <v>605798</v>
+        <v>599696</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" si="0"/>
-        <v>3461087</v>
+        <v>3531965.5</v>
       </c>
       <c r="H8" s="17">
         <f t="shared" si="1"/>
-        <v>453813.51757884986</v>
+        <v>461288.49938167853</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>3007273.48242115</v>
+        <v>3070677.0006183214</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16494,31 +16562,31 @@
         <v>2031</v>
       </c>
       <c r="B9" s="49">
-        <v>395444</v>
+        <v>400473</v>
       </c>
       <c r="C9" s="50">
-        <v>802114.5</v>
+        <v>777526.5</v>
       </c>
       <c r="D9" s="50">
-        <v>1398011.5</v>
+        <v>1448069.5</v>
       </c>
       <c r="E9" s="50">
-        <v>732143.5</v>
+        <v>778887</v>
       </c>
       <c r="F9" s="50">
-        <v>599696</v>
+        <v>592625</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" si="0"/>
-        <v>3531965.5</v>
+        <v>3597108</v>
       </c>
       <c r="H9" s="17">
         <f t="shared" si="1"/>
-        <v>461288.49938167853</v>
+        <v>467154.866966951</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>3070677.0006183214</v>
+        <v>3129953.1330330488</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16527,31 +16595,31 @@
         <v>2032</v>
       </c>
       <c r="B10" s="49">
-        <v>400473</v>
+        <v>404565</v>
       </c>
       <c r="C10" s="50">
-        <v>777526.5</v>
+        <v>748450.5</v>
       </c>
       <c r="D10" s="50">
-        <v>1448069.5</v>
+        <v>1492002</v>
       </c>
       <c r="E10" s="50">
-        <v>778887</v>
+        <v>834141.5</v>
       </c>
       <c r="F10" s="50">
-        <v>592625</v>
+        <v>585355.49999999988</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" si="0"/>
-        <v>3597108</v>
+        <v>3659949.5</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" si="1"/>
-        <v>467154.866966951</v>
+        <v>471928.21676988091</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>3129953.1330330488</v>
+        <v>3188021.2832301189</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16560,31 +16628,31 @@
         <v>2033</v>
       </c>
       <c r="B11" s="49">
-        <v>404565</v>
+        <v>407065</v>
       </c>
       <c r="C11" s="50">
-        <v>748450.5</v>
+        <v>718650</v>
       </c>
       <c r="D11" s="50">
-        <v>1492002</v>
+        <v>1524421.5</v>
       </c>
       <c r="E11" s="50">
-        <v>834141.5</v>
+        <v>895261.5</v>
       </c>
       <c r="F11" s="50">
-        <v>585355.49999999988</v>
+        <v>578769.5</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" si="0"/>
-        <v>3659949.5</v>
+        <v>3717102.5</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" si="1"/>
-        <v>471928.21676988091</v>
+        <v>474844.48619982344</v>
       </c>
       <c r="I11" s="17">
         <f t="shared" si="2"/>
-        <v>3188021.2832301189</v>
+        <v>3242258.0138001768</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16593,31 +16661,31 @@
         <v>2034</v>
       </c>
       <c r="B12" s="49">
-        <v>407065</v>
+        <v>407899</v>
       </c>
       <c r="C12" s="50">
-        <v>718650</v>
+        <v>696049.5</v>
       </c>
       <c r="D12" s="50">
-        <v>1524421.5</v>
+        <v>1544980.5</v>
       </c>
       <c r="E12" s="50">
-        <v>895261.5</v>
+        <v>960380</v>
       </c>
       <c r="F12" s="50">
-        <v>578769.5</v>
+        <v>575063</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" si="0"/>
-        <v>3717102.5</v>
+        <v>3776473</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" si="1"/>
-        <v>474844.48619982344</v>
+        <v>475817.35368165228</v>
       </c>
       <c r="I12" s="17">
         <f t="shared" si="2"/>
-        <v>3242258.0138001768</v>
+        <v>3300655.6463183477</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16626,31 +16694,31 @@
         <v>2035</v>
       </c>
       <c r="B13" s="49">
-        <v>407899</v>
+        <v>407878</v>
       </c>
       <c r="C13" s="50">
-        <v>696049.5</v>
+        <v>687830.5</v>
       </c>
       <c r="D13" s="50">
-        <v>1544980.5000000002</v>
+        <v>1552358.5</v>
       </c>
       <c r="E13" s="50">
-        <v>960380</v>
+        <v>1028185.5</v>
       </c>
       <c r="F13" s="50">
-        <v>575063</v>
+        <v>576512</v>
       </c>
       <c r="G13" s="17">
         <f t="shared" si="0"/>
-        <v>3776473</v>
+        <v>3844886.5</v>
       </c>
       <c r="H13" s="17">
         <f t="shared" si="1"/>
-        <v>475817.35368165228</v>
+        <v>475792.85701844073</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>3300655.6463183477</v>
+        <v>3369093.642981559</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17058,7 +17126,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="yVzq04kMr9DicejtpZk8BCQkGu/ILe/vAL29jrc4BR8OCQ7mXi8m8PGpp8/i+y6YFLEREth9YglcHi74QmAsIA==" saltValue="UcSBdikSReHCRo3I1VnVGw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="iPAybxqXvAfrKFNgt2JYUmaLEvJ0ayzCUhKUo55BpibccFN10kddUfX/Ca5HanfGBeieC4/TDjPBtF1qu4GmOg==" saltValue="jskH4tJ1BOXZmphxIwDNrA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -20855,21 +20923,24 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="XiueAYLUFMUJwG3u7vm9hZORfiGURpk3an7pRU5om47afVXWbOjE+kuRPP3lJP1Dsc1VhTgo03bHwC/Fsb6+Qg==" saltValue="zpSZqo97lUgcKMVUaTln9Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="u201HSnLHibKJLhq+GPDiGe6B6T1/zN3QVxim3CpyA4erR5lDB+x6Vzq3etVEQTTFeZpYlK5PZGF/c1QBPChRg==" saltValue="GdMHy/OErrP5LXM6H5WATg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B28:B30"/>
     <mergeCell ref="B154:B156"/>
     <mergeCell ref="B64:B66"/>
     <mergeCell ref="B95:B97"/>
@@ -20886,22 +20957,19 @@
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B128:B130"/>
     <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B89:B91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -22002,7 +22070,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9u9qva+Fm1PPpoB42swAKbjQsCuvSNIkOBEOoLJH9V9VB53CnjjC9/3VnuGpQUrDjjKskOVpx+fyOAwGOdV0sA==" saltValue="gWAB4+ECRriRyRsQAsbA4w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="p8N2jJHxR9WpweZCXxOPoJCmA5suamhf946yCidQlTkA/jbmhVidngGegWx0ZPyy7xLYdbi0yEbPTQWl40aQUQ==" saltValue="ycov/ORghztU0CaQlx3C/w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -22943,7 +23011,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="KA9sLXkoRJEuKrpfjFxzyeFbQjHR3RzZqOWiFAs82323u9yoauiG5agIDF2rKDOLcReJGfcPmqMgJ4Xp+7HKUQ==" saltValue="4KX/zqYzpw1EDfy/cw07Yg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="14IPncA/re7ZFactD9dKDBew8Xh+c53gvR5aPlF7r7whNXcWMLfYU0XxX3pkeAmD8XAImDFvz4z94rchofzKrw==" saltValue="HjwHOg4lhFLd9utCOn4oVQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -24159,7 +24227,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Ewgr0TaMTQPo+xby4mzYs+/Aw7dfGGc92Qy767J+UN9cEYo4fRmFY9do/cDVZwkBcQtOMklelAN2s1pVcky3NA==" saltValue="H/mG/Wsbgrxo9be3c5O5NA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LbTTw68DqW0xwX6xy6KU+INVwAvIEQYwKEsyi8puOkxO60cFP6j+/GeYXhh6DIH4OpOTi3apEXJdGFB6mNgjaQ==" saltValue="d1YAQKWsJENx1LOfvarmZA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -32294,7 +32362,7 @@
       <c r="I328" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="YFNITOwVDnXKG8Ke8WiRisjzgGHvCmGOJ/BU09kNBLEVCp3D9smzKI219K3fM3cGrlCJvxIkrJxGKh2JUadpPw==" saltValue="bbIcY0wdWuCXD8ZuEx8P+A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="RDqNTIyVFEEQmdNIid9wK1RAEXUBCKLqoFwCRU0XtzZuugtfV8a8RRs0dWdKQ/laxtOGc4zsx+HzIiP06ewj1A==" saltValue="ZMC9gVPw5T+wTtoOoOR5LA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -33588,16 +33656,16 @@
         <v>1</v>
       </c>
       <c r="L33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="M33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="N33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="O33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -33795,16 +33863,20 @@
         <v>1</v>
       </c>
       <c r="L37" s="90">
-        <v>1</v>
+        <f>L31</f>
+        <v>0.38</v>
       </c>
       <c r="M37" s="90">
-        <v>1</v>
+        <f>M31</f>
+        <v>0.38</v>
       </c>
       <c r="N37" s="90">
-        <v>1</v>
+        <f>N31</f>
+        <v>0.38</v>
       </c>
       <c r="O37" s="90">
-        <v>1</v>
+        <f>O31</f>
+        <v>0.38</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -34726,16 +34798,20 @@
         <v>1</v>
       </c>
       <c r="L60" s="90">
-        <v>1</v>
+        <f>L54</f>
+        <v>0.7</v>
       </c>
       <c r="M60" s="90">
-        <v>1</v>
+        <f t="shared" ref="M60:O60" si="16">M54</f>
+        <v>0.7</v>
       </c>
       <c r="N60" s="90">
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.7</v>
       </c>
       <c r="O60" s="90">
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.7</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -34757,39 +34833,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="90">
-        <f t="shared" ref="G61:O61" si="16">IF(G15=1,1,G15*1.05)</f>
+        <f t="shared" ref="G61:O61" si="17">IF(G15=1,1,G15*1.05)</f>
         <v>1</v>
       </c>
       <c r="H61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="I61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="J61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="K61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -34804,11 +34880,11 @@
         <v>200</v>
       </c>
       <c r="C64" s="90">
-        <f t="shared" ref="C64:D67" si="17">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:D67" si="18">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E64" s="90">
@@ -34850,11 +34926,11 @@
         <v>201</v>
       </c>
       <c r="C65" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D65" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E65" s="90">
@@ -34896,11 +34972,11 @@
         <v>202</v>
       </c>
       <c r="C66" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D66" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E66" s="90">
@@ -34942,11 +35018,11 @@
         <v>210</v>
       </c>
       <c r="C67" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D67" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E67" s="90">
@@ -34984,7 +35060,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Bh2Gz2PNe6xvm0BCkxmsrD/fBnnEtXWvDgae8SIjJVwWAWFd662SHkFHHCdkeTXeR0SXKNxmTmROFg0kn/aoUA==" saltValue="mVHkffvXCK+5YgBWt6Y4ow==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ze7ZsL5a4iUa8fpv6i2CVmMLri+sIzVuhfd7evcOxzNY4TYEhdfIMht0ZL8GY4tF8Ug8tMfJM8pqmE/1O9KdjA==" saltValue="8x8nhjwX0KxC2+WledaoZg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -35266,7 +35342,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+MtsajGpieS7tiuKdmTBfe0WiX7502DeVDyXgbxMMu9xYzgZvliFVEV+XKJVpdXYK/B7qP1NWjpQCQYWbLvrqA==" saltValue="YX+ybb84/1nmAJcT9ut6Tw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Tmk2ccGhAZM894usqKa132S2pQsg+420THk3AmA3GjU6TfCc0SEeCelvEarCoFf5QT4v1iTmGVtI2PolxaCz/g==" saltValue="pZ9fmUOdOmwtrifw+h4W7Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -39126,7 +39202,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1Z3FsCghAfgxyyEcZq29cWcmPPscqeEMWFmqR2jlDEem+08pjpCMoW/Dmee4/nxtvEGaLW0kflpoclawU7rGbw==" saltValue="ZhdwxeVwd5kbFKRcqNRdrw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="lUHMYG1y+XIi7xWK3Sm+XLTXWetuHvZWyaChj1rxCvnDNGJ/HBCdH2Rp6y89jCpC7WLFutvDYsHok7xbuXpHYA==" saltValue="LoTg21Ab1Hpc9mu74BavGw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -39766,7 +39842,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="FpQ2a2oJid+HHr1sRXoXcPIGWhiCin62olR/iiikLyzQ4j6vbBy0hj132FAFh9cPCSnkAZ/Sp1ijG15IymXwtA==" saltValue="4Xli9uxwTJ9c5bkBqshdEA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="zFQ+xzUR/4it0r4AlMxDQHlzY3V3LRDOW9JyPHug8xy2HZkOc5XgqUZOS07Lx85P17DqecKd5iXve73lEHRQlw==" saltValue="fG0QTg1C3CMNvU38ojajCg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -40199,7 +40275,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/OoPHg0eAtQ1F2Vnk484rHsSaqaqResa5VzOykyuwkkUT95Pk9KYttFQ7NIsu0UGDR9Qbl7OY06R5CSWlUM3hg==" saltValue="c0mUNsE6zeObo0gEiQclcA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HuHs8523gkll+JXH6LyU7BjjPZHVm5DZ2/9suoihZSoMuqBepJyIXwSEFrr+futNcdtqpKEU4lvULyfTTt9u4g==" saltValue="XGPXALDKLGtMUZ/Csp265w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40618,7 +40694,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="uS3tOKxDHVsyLrtDdFa/HIBXjumgUUS7Uwkp3/ey73/Fui/qwNgvNS3NTwdr4KMzBZMG/3ltnerLAV5uK+jBMQ==" saltValue="IfW5Yd5yUxP721rJS7gc5g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="E/MWYT0/HokFNtWTVV1wGomWn56PfsQE9g30wZpXN74lcgvnG8K7sDUY2v3oxYkpp+e1gGD2xc0vs9/J7+5fbQ==" saltValue="aaITmGT9D9GghKREN9K4Gw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40750,7 +40826,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3bx4TSu4dAB7A73KK1fdBpVOtDNaxEtveYGizpZHfAufpbecLlIlhVj6jsFqaF631YCUQeHvLRzAZNPGsqqMfQ==" saltValue="K0I3HBU7GE1ZUwUuRveBHA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="l2R7J7BWDjFa/YAGVoww3lMU75ixca1RGvI0nPSj5sdUZl2gPEUkJ6pGWycpha6V3tr8rz7dvfTzwx782/jvBQ==" saltValue="q5FLZYSJCcK1Qif8fhzfJA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -40951,7 +41027,7 @@
       <c r="K14" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Q7e4E7naKAQDgsOWWfdoawSskHTufKr/DT7uPpYppb4Vlio1t5D7xxUpO7YBePHASkf6uLxBNq+kTx022ydD4Q==" saltValue="K7kMWdBdtYaSivrWtMPvTQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="YHIhpXMhPqkocnyytx/7FHkpwhyhRiBLE5CDoHjO95z3grtA4/b7HHxV6jcXCWgBxjQT6Bmfz6kPKEoO0dBrEg==" saltValue="tEprihmm7RbQ8+4xf3N8gA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait"/>
 </worksheet>
@@ -41476,7 +41552,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="toWdnVvtg1nhQdm82CGhLNssQoJoicgvTV8ds4B7jd43fLeOv3RX8sN+l7y4FDyRrRy0ScuYeONRLI4bETP9Dg==" saltValue="Fp6VEvVDaxACOHIjIAFsow==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="XdDp0XAZY5QXj42RMRVp+WdEqt4T/31oLmaseaKFxm6YG5rJRFjrxH3USeDiYodpJjA25lJsOXKnpHfGOAYdLA==" saltValue="ofaiOlzdBPyGJ4i6tDM/VQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -41735,7 +41811,7 @@
       <c r="E21" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="CPCHtrztGQ7P7j2eQ0dhlLmVeUaTPP+hJ8Do1JfkK0/D4tT+Bp0WC7ovHusTnE6xD7Mk6wufkv/w+HrZ/ShrKw==" saltValue="KtKsuM0JJsKfWA2LdNKAyQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0+fCHObIcMl4bm7Z+/yqDtHMayEc6bIp+ZqvloIUOWJTis2HfVyOH+G/uXE1OqfPFAvNJUSWOW0C0bumoSmyGw==" saltValue="lweIhBsVpnpVuF6rbWm7pg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -41794,12 +41870,21 @@
       <c r="D3" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="wHkH+tDXgLVEZXB4gjrhtJ1mwqIelxrK24FwvteoKq5RPZlW9uJ1eymIPHBjo5eFrpfRE4FqzTi76EPyEJxVyg==" saltValue="Y877UtOet79EercDycmM6g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4fVLqm2YyL2udY9SbPQsFX9IAG0ZVaWimXdZgeX2hmroE6Vcbfmc1GsdiOp94c33QbSTf+BZggyX0HxoiHfa+Q==" saltValue="sGPlropO4d0syq1q5W1RQg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
@@ -41809,18 +41894,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f77cb9dc30d15950233dec29875e7d3d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c7972fb108f377c3e0c6a81e726e76be" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57ec1f31440e439775915f75cb7954ca">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="62245b0892ab2a20b5f44f74e1fbf663" ns2:_="">
     <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -42003,6 +42079,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA00B2B-FC7F-4ED6-BC3D-3DE83488E245}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1364B1-D0AC-4AFC-8837-019122E84913}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -42012,16 +42096,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA00B2B-FC7F-4ED6-BC3D-3DE83488E245}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89AE9A51-FA73-431C-A4D5-36C1DFA1FEFD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB7E161-F495-494F-94F7-37757C779909}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
